--- a/docs/skin/Skin-Matrix.xlsx
+++ b/docs/skin/Skin-Matrix.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matrix'!$A$1:$H$390</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matrix'!$A$1:$H$395</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H390"/>
+  <dimension ref="A1:H395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -11611,19 +11611,15 @@
           <t>Statistik</t>
         </is>
       </c>
-      <c r="C297" t="inlineStr">
-        <is>
-          <t>:focused</t>
-        </is>
-      </c>
+      <c r="C297" t="inlineStr"/>
       <c r="D297" t="inlineStr">
         <is>
-          <t>.my-table-view:focused</t>
+          <t>.my-table-view .text-field</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -11638,7 +11634,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>"-fx-control-inner-background"</t>
+          <t>"0"</t>
         </is>
       </c>
     </row>
@@ -11653,19 +11649,15 @@
           <t>Statistik</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr">
-        <is>
-          <t>:focused</t>
-        </is>
-      </c>
+      <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
-          <t>.my-table-view:focused</t>
+          <t>.my-table-view .text-field</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -11695,14 +11687,10 @@
           <t>Statistik</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr">
-        <is>
-          <t>:focused</t>
-        </is>
-      </c>
+      <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
-          <t>.my-table-view:focused</t>
+          <t>.my-table-view .text-field</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -11729,57 +11717,69 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Schlagwort — Löschknopf</t>
+          <t>Tabelle</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Tagebuch</t>
-        </is>
-      </c>
-      <c r="C300" t="inlineStr"/>
+          <t>Statistik</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>:focused</t>
+        </is>
+      </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>.tag-chip-remove</t>
+          <t>.my-table-view .text-field:focused</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>playFieldBackground</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>← menuBarBackground</t>
-        </is>
-      </c>
-      <c r="H300" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Schlagwort — Löschknopf</t>
+          <t>Tabelle</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Tagebuch</t>
-        </is>
-      </c>
-      <c r="C301" t="inlineStr"/>
+          <t>Statistik</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>:focused</t>
+        </is>
+      </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>.tag-chip-remove</t>
+          <t>.my-table-view .text-field:focused</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -11794,30 +11794,34 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Color.TRANSPARENT</t>
+          <t>"0"</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Schlagwort — Löschknopf</t>
+          <t>Tabelle</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Tagebuch</t>
-        </is>
-      </c>
-      <c r="C302" t="inlineStr"/>
+          <t>Statistik</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>:focused</t>
+        </is>
+      </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>.tag-chip-remove</t>
+          <t>.my-table-view:focused</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -11832,30 +11836,34 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>"0px"</t>
+          <t>"-fx-control-inner-background"</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Schlagwort — Löschknopf</t>
+          <t>Tabelle</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Tagebuch</t>
-        </is>
-      </c>
-      <c r="C303" t="inlineStr"/>
+          <t>Statistik</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>:focused</t>
+        </is>
+      </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>.tag-chip-remove</t>
+          <t>.my-table-view:focused</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -11870,48 +11878,56 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>"0 0"</t>
+          <t>"0"</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Schlagwort — Löschknopf</t>
+          <t>Tabelle</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Tagebuch</t>
-        </is>
-      </c>
-      <c r="C304" t="inlineStr"/>
+          <t>Statistik</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>:focused</t>
+        </is>
+      </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>.tag-chip-remove .text</t>
+          <t>.my-table-view:focused</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H304" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Tagebuch — Layout</t>
+          <t>Schlagwort — Löschknopf</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -11922,34 +11938,30 @@
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>.diary-viewer-content</t>
+          <t>.tag-chip-remove</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>-fx-spacing</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>playFieldBackground</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>font.getSize() + "px"</t>
-        </is>
-      </c>
+          <t>← menuBarBackground</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Tagebuch — Layout</t>
+          <t>Schlagwort — Löschknopf</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -11960,34 +11972,34 @@
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
-          <t>.diary-viewer-filter-bar</t>
+          <t>.tag-chip-remove</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>-fx-max-width</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>diaryViewerContentWidth</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>diaryViewerContentWidth + "px"</t>
+          <t>Color.TRANSPARENT</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Tagebuch — Layout</t>
+          <t>Schlagwort — Löschknopf</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -11998,34 +12010,34 @@
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
-          <t>.diary-viewer-filter-bar</t>
+          <t>.tag-chip-remove</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>-fx-min-width</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>diaryViewerContentWidth</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>diaryViewerContentWidth + "px"</t>
+          <t>"0px"</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Tagebuch — Layout</t>
+          <t>Schlagwort — Löschknopf</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -12036,30 +12048,34 @@
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
-          <t>.diary-viewer-hint</t>
+          <t>.tag-chip-remove</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>incorrectTextColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H308" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>"0 0"</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Tagebuch — Layout</t>
+          <t>Schlagwort — Löschknopf</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -12070,29 +12086,25 @@
       <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>.diary-viewer-hint</t>
+          <t>.tag-chip-remove .text</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>-fx-font-style</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H309" t="inlineStr">
-        <is>
-          <t>"italic"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -12108,12 +12120,12 @@
       <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
-          <t>.diary-viewer-root</t>
+          <t>.diary-viewer-content</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-spacing</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -12128,7 +12140,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>font.getSize() + "px 0px"</t>
+          <t>font.getSize() + "px"</t>
         </is>
       </c>
     </row>
@@ -12146,27 +12158,27 @@
       <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
-          <t>.diary-viewer-scroll</t>
+          <t>.diary-viewer-filter-bar</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>-fx-background</t>
+          <t>-fx-max-width</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>diaryViewerContentWidth</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>"transparent"</t>
+          <t>diaryViewerContentWidth + "px"</t>
         </is>
       </c>
     </row>
@@ -12184,27 +12196,27 @@
       <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
-          <t>.diary-viewer-scroll</t>
+          <t>.diary-viewer-filter-bar</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-min-width</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>diaryViewerContentWidth</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>"transparent"</t>
+          <t>diaryViewerContentWidth + "px"</t>
         </is>
       </c>
     </row>
@@ -12222,17 +12234,17 @@
       <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
-          <t>.diary-viewer-scroll</t>
+          <t>.diary-viewer-hint</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>incorrectTextColor</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -12240,11 +12252,7 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H313" t="inlineStr">
-        <is>
-          <t>"0 " + font.getSize() * 0.5 + "px 0 0"</t>
-        </is>
-      </c>
+      <c r="H313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -12260,12 +12268,12 @@
       <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
-          <t>.diary-viewer-scroll .viewport</t>
+          <t>.diary-viewer-hint</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-font-style</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -12280,14 +12288,14 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>"transparent"</t>
+          <t>"italic"</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Tagebuchkarte</t>
+          <t>Tagebuch — Layout</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -12298,30 +12306,34 @@
       <c r="C315" t="inlineStr"/>
       <c r="D315" t="inlineStr">
         <is>
-          <t>.diary-card</t>
+          <t>.diary-viewer-root</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>displayTextQuestionBgColor</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>← displayTextBgColor</t>
-        </is>
-      </c>
-      <c r="H315" t="inlineStr"/>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>font.getSize() + "px 0px"</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Tagebuchkarte</t>
+          <t>Tagebuch — Layout</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -12332,34 +12344,34 @@
       <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
-          <t>.diary-card</t>
+          <t>.diary-viewer-scroll</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-background</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>borderBigComponent</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>borderBigComponent.width() + "px"</t>
+          <t>"transparent"</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Tagebuchkarte</t>
+          <t>Tagebuch — Layout</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -12370,34 +12382,34 @@
       <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
-          <t>.diary-card</t>
+          <t>.diary-viewer-scroll</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>-fx-background-radius</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>borderBigComponent</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>borderBigComponent.arc() + "px"</t>
+          <t>"transparent"</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Tagebuchkarte</t>
+          <t>Tagebuch — Layout</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -12408,17 +12420,17 @@
       <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
-          <t>.diary-card</t>
+          <t>.diary-viewer-scroll</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>borderBigComponent</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -12428,14 +12440,14 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>borderBigComponent.color()</t>
+          <t>"0 " + font.getSize() * 0.5 + "px 0 0"</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Tagebuchkarte</t>
+          <t>Tagebuch — Layout</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -12446,27 +12458,27 @@
       <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
-          <t>.diary-card</t>
+          <t>.diary-viewer-scroll .viewport</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>-fx-border-radius</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>borderBigComponent</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>borderBigComponent.arc() + "px"</t>
+          <t>"transparent"</t>
         </is>
       </c>
     </row>
@@ -12489,24 +12501,20 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>borderBigComponent</t>
+          <t>displayTextQuestionBgColor</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>borderBigComponent.width() + "px"</t>
-        </is>
-      </c>
+          <t>← displayTextBgColor</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -12527,22 +12535,22 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>-fx-cursor</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>borderBigComponent</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>"hand"</t>
+          <t>borderBigComponent.width() + "px"</t>
         </is>
       </c>
     </row>
@@ -12565,20 +12573,24 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>-fx-effect</t>
+          <t>-fx-background-radius</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>componentShadow</t>
+          <t>borderBigComponent</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>entfällt</t>
-        </is>
-      </c>
-      <c r="H322" t="inlineStr"/>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>borderBigComponent.arc() + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -12599,12 +12611,12 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>borderBigComponent</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -12614,7 +12626,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>font.getSize() + "px"</t>
+          <t>borderBigComponent.color()</t>
         </is>
       </c>
     </row>
@@ -12632,17 +12644,17 @@
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
-          <t>.diary-card-date</t>
+          <t>.diary-card</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-border-radius</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>borderBigComponent</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -12650,7 +12662,11 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H324" t="inlineStr"/>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>borderBigComponent.arc() + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -12666,27 +12682,27 @@
       <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
-          <t>.diary-card-date</t>
+          <t>.diary-card</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>-fx-font-weight</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>borderBigComponent</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>"bold"</t>
+          <t>borderBigComponent.width() + "px"</t>
         </is>
       </c>
     </row>
@@ -12704,25 +12720,29 @@
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
-          <t>.diary-card-tags</t>
+          <t>.diary-card</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-cursor</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H326" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>"hand"</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -12738,29 +12758,25 @@
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
-          <t>.diary-card-tags</t>
+          <t>.diary-card</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>-fx-font-style</t>
+          <t>-fx-effect</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>componentShadow</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H327" t="inlineStr">
-        <is>
-          <t>"italic"</t>
-        </is>
-      </c>
+          <t>entfällt</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -12776,17 +12792,17 @@
       <c r="C328" t="inlineStr"/>
       <c r="D328" t="inlineStr">
         <is>
-          <t>.diary-card-text</t>
+          <t>.diary-card</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -12794,7 +12810,11 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H328" t="inlineStr"/>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>font.getSize() + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -12807,29 +12827,25 @@
           <t>Tagebuch</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>:hover</t>
-        </is>
-      </c>
+      <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
-          <t>.diary-card:hover</t>
+          <t>.diary-card-date</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>displayTextQuestionBgColor</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>← displayTextBgColor</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H329" t="inlineStr"/>
@@ -12837,7 +12853,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Vorschlagsliste</t>
+          <t>Tagebuchkarte</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -12848,30 +12864,34 @@
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
-          <t>.suggestion-box</t>
+          <t>.diary-card-date</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-font-weight</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>menuBarBackground</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H330" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>"bold"</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Vorschlagsliste</t>
+          <t>Tagebuchkarte</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -12882,17 +12902,17 @@
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
-          <t>.suggestion-box</t>
+          <t>.diary-card-tags</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>borderColor</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -12905,7 +12925,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Vorschlagsliste</t>
+          <t>Tagebuchkarte</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -12916,12 +12936,12 @@
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
-          <t>.suggestion-box</t>
+          <t>.diary-card-tags</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-font-style</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -12936,14 +12956,14 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>"1px"</t>
+          <t>"italic"</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Vorschlagsliste</t>
+          <t>Tagebuchkarte</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -12954,34 +12974,30 @@
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
-          <t>.suggestion-box .label</t>
+          <t>.diary-card-text</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H333" t="inlineStr">
-        <is>
-          <t>"5 5"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Vorschlagsliste</t>
+          <t>Tagebuchkarte</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -12991,12 +13007,12 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>:highlighted</t>
+          <t>:hover</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>.suggestion-box :highlighted</t>
+          <t>.diary-card:hover</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -13006,12 +13022,12 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>menuBarHoverBackground</t>
+          <t>displayTextQuestionBgColor</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>← contrastingShade(menuBarBackground, 20)</t>
+          <t>← displayTextBgColor</t>
         </is>
       </c>
       <c r="H334" t="inlineStr"/>
@@ -13019,28 +13035,28 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Alles (Wurzel)</t>
+          <t>Vorschlagsliste</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>überall</t>
+          <t>Tagebuch</t>
         </is>
       </c>
       <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
         <is>
-          <t>.root</t>
+          <t>.suggestion-box</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>-fx-font-family</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>menuBarBackground</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
@@ -13048,37 +13064,33 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H335" t="inlineStr">
-        <is>
-          <t>"'" + font.getFamily() + "'"</t>
-        </is>
-      </c>
+      <c r="H335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Alles (Wurzel)</t>
+          <t>Vorschlagsliste</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>überall</t>
+          <t>Tagebuch</t>
         </is>
       </c>
       <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
-          <t>.root</t>
+          <t>.suggestion-box</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>-fx-font-size</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>borderColor</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
@@ -13086,95 +13098,103 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H336" t="inlineStr">
-        <is>
-          <t>font.getSize() + "px"</t>
-        </is>
-      </c>
+      <c r="H336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Bildlaufleiste</t>
+          <t>Vorschlagsliste</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>überall</t>
+          <t>Tagebuch</t>
         </is>
       </c>
       <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
-          <t>.scroll-bar .increment-arrow, .scroll-bar .decrement-arrow</t>
+          <t>.suggestion-box</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H337" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>"1px"</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Bildlaufleiste</t>
+          <t>Vorschlagsliste</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>überall</t>
+          <t>Tagebuch</t>
         </is>
       </c>
       <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
-          <t>.scroll-bar .increment-button, .scroll-bar .decrement-button</t>
+          <t>.suggestion-box .label</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>menuBarBackground</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H338" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>"5 5"</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Bildlaufleiste</t>
+          <t>Vorschlagsliste</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>überall</t>
-        </is>
-      </c>
-      <c r="C339" t="inlineStr"/>
+          <t>Tagebuch</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>:highlighted</t>
+        </is>
+      </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>.scroll-bar .thumb</t>
+          <t>.suggestion-box :highlighted</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -13184,12 +13204,12 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>activeComponentBgColor</t>
+          <t>menuBarHoverBackground</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>← contrastingShade(menuBarBackground, 20)</t>
         </is>
       </c>
       <c r="H339" t="inlineStr"/>
@@ -13197,7 +13217,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Bildlaufleiste</t>
+          <t>Alles (Wurzel)</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -13205,24 +13225,20 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>:hover</t>
-        </is>
-      </c>
+      <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
-          <t>.scroll-bar .thumb:hover</t>
+          <t>.root</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-font-family</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>activeComponentHoverColor</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
@@ -13230,12 +13246,16 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H340" t="inlineStr"/>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>"'" + font.getFamily() + "'"</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Bildlaufleiste</t>
+          <t>Alles (Wurzel)</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -13246,34 +13266,34 @@
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
         <is>
-          <t>.scroll-bar .track</t>
+          <t>.root</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-font-size</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>playFieldBackground</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>← menuBarBackground</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>UiUtils.contrastingShade(playFieldBackground,10)</t>
+          <t>font.getSize() + "px"</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Eingabefeld</t>
+          <t>Bildlaufleiste</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -13284,34 +13304,30 @@
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
-          <t>.text-field</t>
+          <t>.scroll-bar .increment-arrow, .scroll-bar .decrement-arrow</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>-fx-alignment</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr">
-        <is>
-          <t>"center"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Eingabefeld</t>
+          <t>Bildlaufleiste</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -13322,7 +13338,7 @@
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
-          <t>.text-field</t>
+          <t>.scroll-bar .increment-button, .scroll-bar .decrement-button</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
@@ -13332,7 +13348,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>activeComponentBgColor</t>
+          <t>menuBarBackground</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -13345,7 +13361,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Eingabefeld</t>
+          <t>Bildlaufleiste</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -13356,17 +13372,17 @@
       <c r="C344" t="inlineStr"/>
       <c r="D344" t="inlineStr">
         <is>
-          <t>.text-field</t>
+          <t>.scroll-bar .thumb</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>borderSmallComponent</t>
+          <t>activeComponentBgColor</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -13374,16 +13390,12 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H344" t="inlineStr">
-        <is>
-          <t>borderSmallComponent.width() + "px"</t>
-        </is>
-      </c>
+      <c r="H344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Eingabefeld</t>
+          <t>Bildlaufleiste</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -13391,20 +13403,24 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C345" t="inlineStr"/>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>:hover</t>
+        </is>
+      </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>.text-field</t>
+          <t>.scroll-bar .thumb:hover</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>-fx-background-radius</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>borderSmallComponent</t>
+          <t>activeComponentHoverColor</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -13412,16 +13428,12 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H345" t="inlineStr">
-        <is>
-          <t>borderSmallComponent.arc() + "px"</t>
-        </is>
-      </c>
+      <c r="H345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Eingabefeld</t>
+          <t>Bildlaufleiste</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -13432,27 +13444,27 @@
       <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
         <is>
-          <t>.text-field</t>
+          <t>.scroll-bar .track</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>borderSmallComponent</t>
+          <t>playFieldBackground</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>← menuBarBackground</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>borderSmallComponent.color()</t>
+          <t>UiUtils.contrastingShade(playFieldBackground,10)</t>
         </is>
       </c>
     </row>
@@ -13475,22 +13487,22 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>-fx-border-radius</t>
+          <t>-fx-alignment</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>borderSmallComponent</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>borderSmallComponent.arc() + "px"</t>
+          <t>"center"</t>
         </is>
       </c>
     </row>
@@ -13513,12 +13525,12 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>borderSmallComponent</t>
+          <t>activeComponentBgColor</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -13526,11 +13538,7 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H348" t="inlineStr">
-        <is>
-          <t>borderSmallComponent.width() + "px"</t>
-        </is>
-      </c>
+      <c r="H348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -13551,20 +13559,24 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>-fx-effect</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>componentShadow</t>
+          <t>borderSmallComponent</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>entfällt</t>
-        </is>
-      </c>
-      <c r="H349" t="inlineStr"/>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>borderSmallComponent.width() + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -13585,7 +13597,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-background-radius</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -13600,7 +13612,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>paddingCss</t>
+          <t>borderSmallComponent.arc() + "px"</t>
         </is>
       </c>
     </row>
@@ -13623,20 +13635,24 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>-fx-text-fill</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>textActiveComponentColor</t>
+          <t>borderSmallComponent</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>← textColor</t>
-        </is>
-      </c>
-      <c r="H351" t="inlineStr"/>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>borderSmallComponent.color()</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -13649,24 +13665,20 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>:disabled</t>
-        </is>
-      </c>
+      <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
         <is>
-          <t>.text-field:disabled</t>
+          <t>.text-field</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-border-radius</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>disabledComponentBgColor</t>
+          <t>borderSmallComponent</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
@@ -13674,7 +13686,11 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H352" t="inlineStr"/>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>borderSmallComponent.arc() + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -13687,19 +13703,15 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>:disabled</t>
-        </is>
-      </c>
+      <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
         <is>
-          <t>.text-field:disabled</t>
+          <t>.text-field</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -13714,7 +13726,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>borderSmallComponent.disabledColor()</t>
+          <t>borderSmallComponent.width() + "px"</t>
         </is>
       </c>
     </row>
@@ -13729,36 +13741,28 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>:disabled</t>
-        </is>
-      </c>
+      <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
         <is>
-          <t>.text-field:disabled</t>
+          <t>.text-field</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-fx-font-weight</t>
+          <t>-fx-effect</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>componentShadow</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>"bold"</t>
-        </is>
-      </c>
+          <t>entfällt</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -13771,34 +13775,30 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>:disabled</t>
-        </is>
-      </c>
+      <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr">
         <is>
-          <t>.text-field:disabled</t>
+          <t>.text-field</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>-fx-opacity</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>borderSmallComponent</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>"1.0"</t>
+          <t>paddingCss</t>
         </is>
       </c>
     </row>
@@ -13813,14 +13813,10 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>:disabled</t>
-        </is>
-      </c>
+      <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
-          <t>.text-field:disabled</t>
+          <t>.text-field</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -13830,12 +13826,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>incorrectTextColor</t>
+          <t>textActiveComponentColor</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>← textColor</t>
         </is>
       </c>
       <c r="H356" t="inlineStr"/>
@@ -13853,27 +13849,27 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>:focused</t>
+          <t>:disabled</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>.text-field:focused</t>
+          <t>.text-field:disabled</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>activeBorderWidth</t>
+          <t>disabledComponentBgColor</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H357" t="inlineStr"/>
@@ -13891,12 +13887,12 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>:focused</t>
+          <t>:disabled</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>.text-field:focused</t>
+          <t>.text-field:disabled</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -13906,15 +13902,19 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>activeBorderColor</t>
+          <t>borderSmallComponent</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>entfällt</t>
-        </is>
-      </c>
-      <c r="H358" t="inlineStr"/>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>borderSmallComponent.disabledColor()</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -13929,30 +13929,34 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>:focused</t>
+          <t>:disabled</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>.text-field:focused</t>
+          <t>.text-field:disabled</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-font-weight</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>activeBorderWidth</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H359" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>"bold"</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -13967,35 +13971,39 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>:invalid-query</t>
+          <t>:disabled</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>.text-field:invalid-query</t>
+          <t>.text-field:disabled</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>-fx-text-fill</t>
+          <t>-fx-opacity</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>incorrectTextColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H360" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>"1.0"</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Jeder Text</t>
+          <t>Eingabefeld</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -14003,20 +14011,24 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr"/>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>:disabled</t>
+        </is>
+      </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>.text</t>
+          <t>.text-field:disabled</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-text-fill</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>incorrectTextColor</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
@@ -14029,7 +14041,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Knopf</t>
+          <t>Eingabefeld</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -14037,25 +14049,29 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C362" t="inlineStr"/>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>:focused</t>
+        </is>
+      </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>.button .text, .date-picker .arrow-button .text</t>
+          <t>.text-field:focused</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>textActiveComponentColor</t>
+          <t>activeBorderWidth</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>← textColor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H362" t="inlineStr"/>
@@ -14063,7 +14079,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Knopf</t>
+          <t>Eingabefeld</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -14071,25 +14087,29 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C363" t="inlineStr"/>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>:focused</t>
+        </is>
+      </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>.button, .date-picker .arrow-button, .spinner .increment-arrow-button, .spinner .decrement-arrow-button</t>
+          <t>.text-field:focused</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>activeComponentBgColor</t>
+          <t>activeBorderColor</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>entfällt</t>
         </is>
       </c>
       <c r="H363" t="inlineStr"/>
@@ -14097,7 +14117,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Knopf</t>
+          <t>Eingabefeld</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -14105,37 +14125,37 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C364" t="inlineStr"/>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>:focused</t>
+        </is>
+      </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>.button, .date-picker .arrow-button, .spinner .increment-arrow-button, .spinner .decrement-arrow-button</t>
+          <t>.text-field:focused</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>borderSmallComponent</t>
+          <t>activeBorderWidth</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H364" t="inlineStr">
-        <is>
-          <t>borderSmallComponent.width() + "px"</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Knopf</t>
+          <t>Eingabefeld</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -14143,20 +14163,24 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C365" t="inlineStr"/>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>:invalid-query</t>
+        </is>
+      </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>.button, .date-picker .arrow-button, .spinner .increment-arrow-button, .spinner .decrement-arrow-button</t>
+          <t>.text-field:invalid-query</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>-fx-background-radius</t>
+          <t>-fx-text-fill</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>borderSmallComponent</t>
+          <t>incorrectTextColor</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
@@ -14164,16 +14188,12 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H365" t="inlineStr">
-        <is>
-          <t>borderSmallComponent.arc() + "px"</t>
-        </is>
-      </c>
+      <c r="H365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Knopf</t>
+          <t>Jeder Text</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -14184,17 +14204,17 @@
       <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
-          <t>.button, .date-picker .arrow-button, .spinner .increment-arrow-button, .spinner .decrement-arrow-button</t>
+          <t>.text</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>borderSmallComponent</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
@@ -14202,11 +14222,7 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H366" t="inlineStr">
-        <is>
-          <t>borderSmallComponent.color()</t>
-        </is>
-      </c>
+      <c r="H366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -14222,29 +14238,25 @@
       <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
-          <t>.button, .date-picker .arrow-button, .spinner .increment-arrow-button, .spinner .decrement-arrow-button</t>
+          <t>.button .text, .date-picker .arrow-button .text</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>-fx-border-radius</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>borderSmallComponent</t>
+          <t>textActiveComponentColor</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H367" t="inlineStr">
-        <is>
-          <t>borderSmallComponent.arc() + "px"</t>
-        </is>
-      </c>
+          <t>← textColor</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -14265,12 +14277,12 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>borderSmallComponent</t>
+          <t>activeComponentBgColor</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
@@ -14278,11 +14290,7 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H368" t="inlineStr">
-        <is>
-          <t>borderSmallComponent.width() + "px"</t>
-        </is>
-      </c>
+      <c r="H368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -14303,20 +14311,24 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>-fx-effect</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>componentShadow</t>
+          <t>borderSmallComponent</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>entfällt</t>
-        </is>
-      </c>
-      <c r="H369" t="inlineStr"/>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>borderSmallComponent.width() + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -14329,24 +14341,20 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C370" t="inlineStr">
-        <is>
-          <t>:hover, :hover</t>
-        </is>
-      </c>
+      <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
-          <t>.button:hover, .date-picker .arrow-button:hover</t>
+          <t>.button, .date-picker .arrow-button, .spinner .increment-arrow-button, .spinner .decrement-arrow-button</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-background-radius</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>activeComponentHoverColor</t>
+          <t>borderSmallComponent</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
@@ -14354,7 +14362,11 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H370" t="inlineStr"/>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>borderSmallComponent.arc() + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -14367,24 +14379,20 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C371" t="inlineStr">
-        <is>
-          <t>:pressed, :pressed</t>
-        </is>
-      </c>
+      <c r="C371" t="inlineStr"/>
       <c r="D371" t="inlineStr">
         <is>
-          <t>.button:pressed, .date-picker .arrow-button:pressed</t>
+          <t>.button, .date-picker .arrow-button, .spinner .increment-arrow-button, .spinner .decrement-arrow-button</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>activeComponentHoverColor</t>
+          <t>borderSmallComponent</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
@@ -14394,14 +14402,14 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>UiUtils.contrastingShade(activeComponentHoverColor, 8)</t>
+          <t>borderSmallComponent.color()</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Menü</t>
+          <t>Knopf</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -14412,17 +14420,17 @@
       <c r="C372" t="inlineStr"/>
       <c r="D372" t="inlineStr">
         <is>
-          <t>.context-menu</t>
+          <t>.button, .date-picker .arrow-button, .spinner .increment-arrow-button, .spinner .decrement-arrow-button</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-border-radius</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>menuBarBackground</t>
+          <t>borderSmallComponent</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -14430,12 +14438,16 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H372" t="inlineStr"/>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>borderSmallComponent.arc() + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Menü</t>
+          <t>Knopf</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -14446,17 +14458,17 @@
       <c r="C373" t="inlineStr"/>
       <c r="D373" t="inlineStr">
         <is>
-          <t>.context-menu</t>
+          <t>.button, .date-picker .arrow-button, .spinner .increment-arrow-button, .spinner .decrement-arrow-button</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>thinBorderColor</t>
+          <t>borderSmallComponent</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
@@ -14464,12 +14476,16 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H373" t="inlineStr"/>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>borderSmallComponent.width() + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Menü</t>
+          <t>Knopf</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -14480,34 +14496,30 @@
       <c r="C374" t="inlineStr"/>
       <c r="D374" t="inlineStr">
         <is>
-          <t>.context-menu</t>
+          <t>.button, .date-picker .arrow-button, .spinner .increment-arrow-button, .spinner .decrement-arrow-button</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-effect</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>thinBorderWidth</t>
+          <t>componentShadow</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H374" t="inlineStr">
-        <is>
-          <t>thinBorderWidth + "px"</t>
-        </is>
-      </c>
+          <t>entfällt</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Menü</t>
+          <t>Knopf</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -14515,10 +14527,14 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C375" t="inlineStr"/>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>:hover, :hover</t>
+        </is>
+      </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>.menu-bar</t>
+          <t>.button:hover, .date-picker .arrow-button:hover</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
@@ -14528,7 +14544,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>menuBarBackground</t>
+          <t>activeComponentHoverColor</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
@@ -14541,7 +14557,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Menü</t>
+          <t>Knopf</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -14549,28 +14565,36 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C376" t="inlineStr"/>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>:pressed, :pressed</t>
+        </is>
+      </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>.menu-button</t>
+          <t>.button:pressed, .date-picker .arrow-button:pressed</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>menuButtonPadding</t>
+          <t>activeComponentHoverColor</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>← font × 0,3 / 0,4</t>
-        </is>
-      </c>
-      <c r="H376" t="inlineStr"/>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>UiUtils.contrastingShade(activeComponentHoverColor, 8)</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -14586,17 +14610,17 @@
       <c r="C377" t="inlineStr"/>
       <c r="D377" t="inlineStr">
         <is>
-          <t>.menu-item</t>
+          <t>.context-menu</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>-fx-font-family</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>menuBarBackground</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
@@ -14604,11 +14628,7 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H377" t="inlineStr">
-        <is>
-          <t>"'" + font.getFamily() + "'"</t>
-        </is>
-      </c>
+      <c r="H377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -14624,22 +14644,22 @@
       <c r="C378" t="inlineStr"/>
       <c r="D378" t="inlineStr">
         <is>
-          <t>.menu-item</t>
+          <t>.context-menu</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>menuItemPadding</t>
+          <t>thinBorderColor</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>← font × 0,1 / 0,5</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H378" t="inlineStr"/>
@@ -14655,32 +14675,32 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>:disabled</t>
-        </is>
-      </c>
+      <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
-          <t>.menu-item:disabled .label</t>
+          <t>.context-menu</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>-fx-text-fill</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>thinBorderWidth</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H379" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>thinBorderWidth + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -14693,14 +14713,10 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>:disabled, :hover</t>
-        </is>
-      </c>
+      <c r="C380" t="inlineStr"/>
       <c r="D380" t="inlineStr">
         <is>
-          <t>.menu-item:disabled:hover</t>
+          <t>.menu-bar</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -14710,19 +14726,15 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>menuBarBackground</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H380" t="inlineStr">
-        <is>
-          <t>"transparent"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -14735,29 +14747,25 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C381" t="inlineStr">
-        <is>
-          <t>:focused</t>
-        </is>
-      </c>
+      <c r="C381" t="inlineStr"/>
       <c r="D381" t="inlineStr">
         <is>
-          <t>.menu-item:focused</t>
+          <t>.menu-button</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>menuBarHoverBackground</t>
+          <t>menuButtonPadding</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>← contrastingShade(menuBarBackground, 20)</t>
+          <t>← font × 0,3 / 0,4</t>
         </is>
       </c>
       <c r="H381" t="inlineStr"/>
@@ -14773,32 +14781,32 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C382" t="inlineStr">
-        <is>
-          <t>:hover</t>
-        </is>
-      </c>
+      <c r="C382" t="inlineStr"/>
       <c r="D382" t="inlineStr">
         <is>
-          <t>.menu-item:hover</t>
+          <t>.menu-item</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-font-family</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>menuBarHoverBackground</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>← contrastingShade(menuBarBackground, 20)</t>
-        </is>
-      </c>
-      <c r="H382" t="inlineStr"/>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>"'" + font.getFamily() + "'"</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -14811,29 +14819,25 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C383" t="inlineStr">
-        <is>
-          <t>:hover</t>
-        </is>
-      </c>
+      <c r="C383" t="inlineStr"/>
       <c r="D383" t="inlineStr">
         <is>
-          <t>.menu:hover</t>
+          <t>.menu-item</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>menuBarHoverBackground</t>
+          <t>menuItemPadding</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>← contrastingShade(menuBarBackground, 20)</t>
+          <t>← font × 0,1 / 0,5</t>
         </is>
       </c>
       <c r="H383" t="inlineStr"/>
@@ -14851,27 +14855,27 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>:showing</t>
+          <t>:disabled</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>.menu:showing</t>
+          <t>.menu-item:disabled .label</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-text-fill</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>menuBarHoverBackground</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>← contrastingShade(menuBarBackground, 20)</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H384" t="inlineStr"/>
@@ -14887,15 +14891,19 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C385" t="inlineStr"/>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>:disabled, :hover</t>
+        </is>
+      </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>.my-spacer</t>
+          <t>.menu-item:disabled:hover</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>-fx-opacity</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -14910,7 +14918,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>"0"</t>
+          <t>"transparent"</t>
         </is>
       </c>
     </row>
@@ -14925,37 +14933,37 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C386" t="inlineStr"/>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>:focused</t>
+        </is>
+      </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>.my-spacer</t>
+          <t>.menu-item:focused</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>-fx-pref-height</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>menuBarHoverBackground</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H386" t="inlineStr">
-        <is>
-          <t>"" + font.getSize() * 0.3 + "px"</t>
-        </is>
-      </c>
+          <t>← contrastingShade(menuBarBackground, 20)</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Titelleiste des Hauptfensters</t>
+          <t>Menü</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -14963,10 +14971,14 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C387" t="inlineStr"/>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>:hover</t>
+        </is>
+      </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>.my-header-bar</t>
+          <t>.menu-item:hover</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
@@ -14976,12 +14988,12 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>menuBarBackground</t>
+          <t>menuBarHoverBackground</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>← contrastingShade(menuBarBackground, 20)</t>
         </is>
       </c>
       <c r="H387" t="inlineStr"/>
@@ -14989,7 +15001,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Titelleiste des Hauptfensters</t>
+          <t>Menü</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -14997,25 +15009,29 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C388" t="inlineStr"/>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>:hover</t>
+        </is>
+      </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>.my-header-bar</t>
+          <t>.menu:hover</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>thinBorderColor</t>
+          <t>menuBarHoverBackground</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>← contrastingShade(menuBarBackground, 20)</t>
         </is>
       </c>
       <c r="H388" t="inlineStr"/>
@@ -15023,7 +15039,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Titelleiste des Hauptfensters</t>
+          <t>Menü</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -15031,37 +15047,37 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C389" t="inlineStr"/>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>:showing</t>
+        </is>
+      </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>.my-header-bar</t>
+          <t>.menu:showing</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>menuBarHoverBackground</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H389" t="inlineStr">
-        <is>
-          <t>"0 0 1 0"</t>
-        </is>
-      </c>
+          <t>← contrastingShade(menuBarBackground, 20)</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Titelleiste des Hauptfensters</t>
+          <t>Menü</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -15072,32 +15088,214 @@
       <c r="C390" t="inlineStr"/>
       <c r="D390" t="inlineStr">
         <is>
+          <t>.my-spacer</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>-fx-opacity</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Menü</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>überall</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>.my-spacer</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>-fx-pref-height</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>font</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>"" + font.getSize() * 0.3 + "px"</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Titelleiste des Hauptfensters</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>überall</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>.my-header-bar</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>-fx-background-color</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>menuBarBackground</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Titelleiste des Hauptfensters</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>überall</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>.my-header-bar</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>-fx-border-color</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>thinBorderColor</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Titelleiste des Hauptfensters</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>überall</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>.my-header-bar</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>-fx-border-width</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>"0 0 1 0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Titelleiste des Hauptfensters</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>überall</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
           <t>.my-header-leading</t>
         </is>
       </c>
-      <c r="E390" t="inlineStr">
+      <c r="E395" t="inlineStr">
         <is>
           <t>-fx-padding</t>
         </is>
       </c>
-      <c r="F390" t="inlineStr">
+      <c r="F395" t="inlineStr">
         <is>
           <t>font</t>
         </is>
       </c>
-      <c r="G390" t="inlineStr">
-        <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H390" t="inlineStr">
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
         <is>
           <t>"0 0 0 " + (font.getSize() * 0.5) + "px"</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H390"/>
+  <autoFilter ref="A1:H395"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/skin/Skin-Matrix.xlsx
+++ b/docs/skin/Skin-Matrix.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matrix'!$A$1:$H$417</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Matrix'!$A$1:$H$419</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H417"/>
+  <dimension ref="A1:H419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4879,22 +4879,22 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>-fx-spacing</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>font.getSize() * 0.5 + "px"</t>
+          <t>schattenPolster</t>
         </is>
       </c>
     </row>
@@ -4912,12 +4912,12 @@
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
-          <t>.movie-viewer-root</t>
+          <t>.movie-viewer-results</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-spacing</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4932,7 +4932,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>padding + "px"</t>
+          <t>Math.max(padding * 0.5, schatten.bottom()) + "px"</t>
         </is>
       </c>
     </row>
@@ -4950,27 +4950,27 @@
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
-          <t>.movie-viewer-scroll</t>
+          <t>.movie-viewer-root</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>-fx-background</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>"transparent"</t>
+          <t>padding + "px"</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-background</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5031,22 +5031,22 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>padding * 0.5 + "px"</t>
+          <t>"transparent"</t>
         </is>
       </c>
     </row>
@@ -5064,27 +5064,27 @@
       <c r="C126" t="inlineStr"/>
       <c r="D126" t="inlineStr">
         <is>
-          <t>.movie-viewer-scroll .viewport</t>
+          <t>.movie-viewer-scroll</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>"transparent"</t>
+          <t>padding * 0.5 + "px"</t>
         </is>
       </c>
     </row>
@@ -5102,27 +5102,27 @@
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr">
         <is>
-          <t>.movie-viewer-swyt</t>
+          <t>.movie-viewer-scroll .viewport</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>-fx-max-width</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>movieViewerSwytPercent</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20 — Prozent der contentSize</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>swytBreite + "px"</t>
+          <t>"transparent"</t>
         </is>
       </c>
     </row>
@@ -5150,12 +5150,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>contentSize</t>
+          <t>movieViewerSwytPercent</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>1910 × 1000 — aus der Datei nicht setzbar</t>
+          <t>20 — Prozent der contentSize</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -5183,17 +5183,17 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>-fx-min-width</t>
+          <t>-fx-max-width</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>movieViewerSwytPercent</t>
+          <t>contentSize</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20 — Prozent der contentSize</t>
+          <t>1910 × 1000 — aus der Datei nicht setzbar</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>contentSize</t>
+          <t>movieViewerSwytPercent</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>1910 × 1000 — aus der Datei nicht setzbar</t>
+          <t>20 — Prozent der contentSize</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5259,22 +5259,22 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-min-width</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>contentSize</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>1910 × 1000 — aus der Datei nicht setzbar</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>"0"</t>
+          <t>swytBreite + "px"</t>
         </is>
       </c>
     </row>
@@ -5297,22 +5297,22 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>-fx-pref-width</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>movieViewerSwytPercent</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20 — Prozent der contentSize</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>swytBreite + "px"</t>
+          <t>"0"</t>
         </is>
       </c>
     </row>
@@ -5340,12 +5340,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>contentSize</t>
+          <t>movieViewerSwytPercent</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>1910 × 1000 — aus der Datei nicht setzbar</t>
+          <t>20 — Prozent der contentSize</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -5373,22 +5373,22 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>-fx-spacing</t>
+          <t>-fx-pref-width</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>contentSize</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>1910 × 1000 — aus der Datei nicht setzbar</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>padding * 0.8 + "px"</t>
+          <t>swytBreite + "px"</t>
         </is>
       </c>
     </row>
@@ -5406,17 +5406,17 @@
       <c r="C135" t="inlineStr"/>
       <c r="D135" t="inlineStr">
         <is>
-          <t>.movie-viewer-swyt .label</t>
+          <t>.movie-viewer-swyt</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-spacing</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5424,12 +5424,16 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>padding * 0.8 + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Filmkarte</t>
+          <t>Film — Layout</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -5440,7 +5444,7 @@
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr">
         <is>
-          <t>.movie-card-header .text</t>
+          <t>.movie-viewer-swyt .label</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5479,24 +5483,20 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>-fx-font-weight</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>"bold"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5512,12 +5512,12 @@
       <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
-          <t>.movie-card-link</t>
+          <t>.movie-card-header .text</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>-fx-cursor</t>
+          <t>-fx-font-weight</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>"hand"</t>
+          <t>"bold"</t>
         </is>
       </c>
     </row>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>-fx-underline</t>
+          <t>-fx-cursor</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>"true"</t>
+          <t>"hand"</t>
         </is>
       </c>
     </row>
@@ -5588,25 +5588,29 @@
       <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>.movie-card-link .text</t>
+          <t>.movie-card-link</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-underline</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>"true"</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5622,29 +5626,25 @@
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
-          <t>.movie-card-rating</t>
+          <t>.movie-card-link .text</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>-fx-alignment</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>"center"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5665,22 +5665,22 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>-fx-font-size</t>
+          <t>-fx-alignment</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>moviePosterWidth</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(int)(moviePosterWidth * 0.5) + "px"</t>
+          <t>"center"</t>
         </is>
       </c>
     </row>
@@ -5703,22 +5703,22 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>-fx-font-weight</t>
+          <t>-fx-font-size</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>moviePosterWidth</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>"bold"</t>
+          <t>(int)(moviePosterWidth * 0.5) + "px"</t>
         </is>
       </c>
     </row>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-font-weight</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>"0"</t>
+          <t>"bold"</t>
         </is>
       </c>
     </row>
@@ -5774,25 +5774,29 @@
       <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>.movie-card-rating .text</t>
+          <t>.movie-card-rating</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5808,7 +5812,7 @@
       <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>.movie-card-text .text</t>
+          <t>.movie-card-rating .text</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5831,37 +5835,33 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Antwortfeld (Fast Write)</t>
+          <t>Filmkarte</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Lernen</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>:active</t>
-        </is>
-      </c>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>.my-answer-slot:active</t>
+          <t>.movie-card-text .text</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>answerSlotWaitingBgColor</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>← activeComponentBgColor 10% zu playFieldBackground</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
@@ -5889,24 +5889,20 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>borderSmallComponent</t>
+          <t>answerSlotWaitingBgColor</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>borderSmallComponent.width()</t>
-        </is>
-      </c>
+          <t>← activeComponentBgColor 10% zu playFieldBackground</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5931,7 +5927,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5946,7 +5942,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>borderSmallComponent.color()</t>
+          <t>borderSmallComponent.width()</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5969,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5988,14 +5984,14 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>borderSmallComponent.width()</t>
+          <t>borderSmallComponent.color()</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Antwortknopf (Multiple Choice)</t>
+          <t>Antwortfeld (Fast Write)</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6003,15 +5999,19 @@
           <t>Lernen</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>:active</t>
+        </is>
+      </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>.my-mc-button</t>
+          <t>.my-answer-slot:active</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>paddingCss</t>
+          <t>borderSmallComponent.width()</t>
         </is>
       </c>
     </row>
@@ -6041,24 +6041,20 @@
           <t>Lernen</t>
         </is>
       </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>:active</t>
-        </is>
-      </c>
+      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>.my-mc-button:active</t>
+          <t>.my-mc-button</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>activeComponentBgColor</t>
+          <t>borderSmallComponent</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -6066,7 +6062,11 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>paddingCss</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6091,17 +6091,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>activeBorderWidth</t>
+          <t>activeComponentBgColor</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H153" t="inlineStr"/>
@@ -6129,17 +6129,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>activeBorderColor</t>
+          <t>activeBorderWidth</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>entfällt</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
@@ -6167,17 +6167,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>activeBorderWidth</t>
+          <t>activeBorderColor</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>entfällt</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
@@ -6195,27 +6195,27 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>:active, :hover</t>
+          <t>:active</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>.my-mc-button:active:hover</t>
+          <t>.my-mc-button:active</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>activeComponentHoverColor</t>
+          <t>activeBorderWidth</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
@@ -6233,12 +6233,12 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>:active, :pressed</t>
+          <t>:active, :hover</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>.my-mc-button:active:pressed</t>
+          <t>.my-mc-button:active:hover</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -6256,11 +6256,7 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>UiUtils.contrastingShade(activeComponentHoverColor, 8)</t>
-        </is>
-      </c>
+      <c r="H157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6275,12 +6271,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>:correct</t>
+          <t>:active, :pressed</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>.my-mc-button:correct</t>
+          <t>.my-mc-button:active:pressed</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -6290,7 +6286,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>activeComponentBgColor</t>
+          <t>activeComponentHoverColor</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -6300,7 +6296,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>correctFlaeche</t>
+          <t>UiUtils.contrastingShade(activeComponentHoverColor, 8)</t>
         </is>
       </c>
     </row>
@@ -6332,12 +6328,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>mcResultBorderWidth</t>
+          <t>activeComponentBgColor</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6416,12 +6412,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>correctColor</t>
+          <t>mcResultBorderWidth</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6453,20 +6449,24 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>mcResultBorderWidth</t>
+          <t>correctColor</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr"/>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>correctFlaeche</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6504,11 +6504,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>mcResultBorderWidth &gt; 0 ? correctColor : null</t>
-        </is>
-      </c>
+      <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6538,12 +6534,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>correctColor</t>
+          <t>mcResultBorderWidth</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6575,20 +6571,24 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>mcResultBorderWidth</t>
+          <t>correctColor</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr"/>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>mcResultBorderWidth &gt; 0 ? correctColor : null</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6608,22 +6608,22 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>.my-mc-button:correct .text</t>
+          <t>.my-mc-button:correct</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>mcCorrectTextColor</t>
+          <t>mcResultBorderWidth</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>entfällt</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H166" t="inlineStr"/>
@@ -6641,27 +6641,27 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>:inactive</t>
+          <t>:correct</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>.my-mc-button:inactive</t>
+          <t>.my-mc-button:correct .text</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>disabledComponentBgColor</t>
+          <t>mcCorrectTextColor</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>entfällt</t>
         </is>
       </c>
       <c r="H167" t="inlineStr"/>
@@ -6679,12 +6679,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>:incorrect</t>
+          <t>:inactive</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>.my-mc-button:incorrect</t>
+          <t>.my-mc-button:inactive</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>activeComponentBgColor</t>
+          <t>disabledComponentBgColor</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -6702,11 +6702,7 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>incorrectFlaeche</t>
-        </is>
-      </c>
+      <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6736,12 +6732,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>mcResultBorderWidth</t>
+          <t>activeComponentBgColor</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -6820,12 +6816,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>incorrectColor</t>
+          <t>mcResultBorderWidth</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -6857,20 +6853,24 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>mcResultBorderWidth</t>
+          <t>incorrectColor</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H172" t="inlineStr"/>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>incorrectFlaeche</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6908,11 +6908,7 @@
           <t>0</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
-        <is>
-          <t>mcResultBorderWidth &gt; 0 ? incorrectColor : null</t>
-        </is>
-      </c>
+      <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6942,12 +6938,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>incorrectColor</t>
+          <t>mcResultBorderWidth</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -6979,20 +6975,24 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>mcResultBorderWidth</t>
+          <t>incorrectColor</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H175" t="inlineStr"/>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>mcResultBorderWidth &gt; 0 ? incorrectColor : null</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7012,22 +7012,22 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>.my-mc-button:incorrect .text</t>
+          <t>.my-mc-button:incorrect</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>mcIncorrectTextColor</t>
+          <t>mcResultBorderWidth</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>entfällt</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
@@ -7045,34 +7045,30 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>:squeezed</t>
+          <t>:incorrect</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>.my-mc-button:squeezed</t>
+          <t>.my-mc-button:incorrect .text</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>-fx-line-spacing</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>mcIncorrectTextColor</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>lineSpacingSqueezed + "px"</t>
-        </is>
-      </c>
+          <t>entfällt</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7097,12 +7093,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-line-spacing</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>borderSmallComponent</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -7112,7 +7108,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>squeezedPadding</t>
+          <t>lineSpacingSqueezed + "px"</t>
         </is>
       </c>
     </row>
@@ -7139,22 +7135,22 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>-fx-text-alignment</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>borderSmallComponent</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>"center"</t>
+          <t>squeezedPadding</t>
         </is>
       </c>
     </row>
@@ -7181,7 +7177,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>-fx-wrap-text</t>
+          <t>-fx-text-alignment</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -7196,7 +7192,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>"true"</t>
+          <t>"center"</t>
         </is>
       </c>
     </row>
@@ -7213,32 +7209,32 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>:tiny</t>
+          <t>:squeezed</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>.my-mc-button:tiny</t>
+          <t>.my-mc-button:squeezed</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>-fx-font-size</t>
+          <t>-fx-wrap-text</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>smallFont</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>smallFont.getSize() + "px"</t>
+          <t>"true"</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7261,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>-fx-line-spacing</t>
+          <t>-fx-font-size</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -7280,7 +7276,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>lineSpacingTiny + "px"</t>
+          <t>smallFont.getSize() + "px"</t>
         </is>
       </c>
     </row>
@@ -7307,12 +7303,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-line-spacing</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>borderSmallComponent</t>
+          <t>smallFont</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -7322,7 +7318,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>squeezedPadding</t>
+          <t>lineSpacingTiny + "px"</t>
         </is>
       </c>
     </row>
@@ -7349,29 +7345,29 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>-fx-wrap-text</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>borderSmallComponent</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>"true"</t>
+          <t>squeezedPadding</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Bild-Karte — Fläche</t>
+          <t>Antwortknopf (Multiple Choice)</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -7379,28 +7375,36 @@
           <t>Lernen</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr"/>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>:tiny</t>
+        </is>
+      </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>.my-image-map-pane</t>
+          <t>.my-mc-button:tiny</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>-fx-effect</t>
+          <t>-fx-wrap-text</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>componentShadow</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>entfällt</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>"true"</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7416,29 +7420,25 @@
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr">
         <is>
-          <t>.my-image-map-pane #borderOverlay</t>
+          <t>.my-image-map-pane</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-effect</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>borderBigComponent</t>
+          <t>componentShadow</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>borderBigComponent.width() + "px"</t>
-        </is>
-      </c>
+          <t>entfällt</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>borderBigComponent.color()</t>
+          <t>borderBigComponent.width() + "px"</t>
         </is>
       </c>
     </row>
@@ -7497,7 +7497,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>-fx-border-radius</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(borderBigComponent.arc()) + "px"</t>
+          <t>borderBigComponent.color()</t>
         </is>
       </c>
     </row>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-border-radius</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -7550,14 +7550,14 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>borderBigComponent.width() + "px"</t>
+          <t>(borderBigComponent.arc()) + "px"</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Bild-Karte — Form</t>
+          <t>Bild-Karte — Fläche</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -7565,24 +7565,20 @@
           <t>Lernen</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>:correct</t>
-        </is>
-      </c>
+      <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
-          <t>.my-image-map-shape:correct .first</t>
+          <t>.my-image-map-pane #borderOverlay</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>correctColor</t>
+          <t>borderBigComponent</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -7590,7 +7586,11 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr"/>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>borderBigComponent.width() + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7610,22 +7610,22 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>.my-image-map-shape:correct .second</t>
+          <t>.my-image-map-shape:correct .first</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>-fx-stroke</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>borderShapeColor</t>
+          <t>correctColor</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>← borderColor</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H191" t="inlineStr"/>
@@ -7648,29 +7648,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>.my-image-map-shape:correct.river .first</t>
+          <t>.my-image-map-shape:correct .second</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-stroke</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>borderShapeColor</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>"transparent"</t>
-        </is>
-      </c>
+          <t>← borderColor</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7695,20 +7691,24 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>-fx-stroke</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>borderShapeColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>← borderColor</t>
-        </is>
-      </c>
-      <c r="H193" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>"transparent"</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7733,24 +7733,20 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>-fx-stroke-width</t>
+          <t>-fx-stroke</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>imageMapShapeMarkedOuterWidth</t>
+          <t>borderShapeColor</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>imageMapShapeMarkedOuterWidth + "px"</t>
-        </is>
-      </c>
+          <t>← borderColor</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7770,27 +7766,27 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>.my-image-map-shape:correct.river .second</t>
+          <t>.my-image-map-shape:correct.river .first</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-stroke-width</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>imageMapShapeMarkedOuterWidth</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>"transparent"</t>
+          <t>imageMapShapeMarkedOuterWidth + "px"</t>
         </is>
       </c>
     </row>
@@ -7817,20 +7813,24 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>-fx-stroke</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>correctColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H196" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>"transparent"</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7855,24 +7855,20 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>-fx-stroke-width</t>
+          <t>-fx-stroke</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>imageMapShapeMarkedInnerWidth</t>
+          <t>correctColor</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>imageMapShapeMarkedInnerWidth + "px"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7887,30 +7883,34 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>:incorrect</t>
+          <t>:correct</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>.my-image-map-shape:incorrect .first</t>
+          <t>.my-image-map-shape:correct.river .second</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-stroke-width</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>incorrectColor</t>
+          <t>imageMapShapeMarkedInnerWidth</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H198" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>imageMapShapeMarkedInnerWidth + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7930,22 +7930,22 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>.my-image-map-shape:incorrect .second</t>
+          <t>.my-image-map-shape:incorrect .first</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>-fx-stroke</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>borderShapeColor</t>
+          <t>incorrectColor</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>← borderColor</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H199" t="inlineStr"/>
@@ -7963,34 +7963,30 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>:marked</t>
+          <t>:incorrect</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>.my-image-map-shape:marked .first</t>
+          <t>.my-image-map-shape:incorrect .second</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-stroke</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>borderShapeColor</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>"transparent"</t>
-        </is>
-      </c>
+          <t>← borderColor</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8015,20 +8011,24 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>-fx-stroke</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>borderShapeColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>← borderColor</t>
-        </is>
-      </c>
-      <c r="H201" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>"transparent"</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8053,24 +8053,20 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>-fx-stroke-width</t>
+          <t>-fx-stroke</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>imageMapShapeMarkedOuterWidth</t>
+          <t>borderShapeColor</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>imageMapShapeMarkedOuterWidth + "px"</t>
-        </is>
-      </c>
+          <t>← borderColor</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -8090,27 +8086,27 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>.my-image-map-shape:marked .second</t>
+          <t>.my-image-map-shape:marked .first</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-stroke-width</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>imageMapShapeMarkedOuterWidth</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>"transparent"</t>
+          <t>imageMapShapeMarkedOuterWidth + "px"</t>
         </is>
       </c>
     </row>
@@ -8137,20 +8133,24 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>-fx-stroke</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>markedColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H204" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>"transparent"</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -8175,29 +8175,25 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>-fx-stroke-width</t>
+          <t>-fx-stroke</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>imageMapShapeMarkedInnerWidth</t>
+          <t>markedColor</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>imageMapShapeMarkedInnerWidth + "px"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Bild-Karte — Klickschicht</t>
+          <t>Bild-Karte — Form</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -8205,30 +8201,34 @@
           <t>Lernen</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr"/>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>:marked</t>
+        </is>
+      </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>.first</t>
+          <t>.my-image-map-shape:marked .second</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-stroke-width</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>imageMapShapeMarkedInnerWidth</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>"transparent"</t>
+          <t>imageMapShapeMarkedInnerWidth + "px"</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>-fx-stroke</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -8289,7 +8289,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>-fx-stroke-line-cap</t>
+          <t>-fx-stroke</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>"round"</t>
+          <t>"transparent"</t>
         </is>
       </c>
     </row>
@@ -8327,7 +8327,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>-fx-stroke-line-join</t>
+          <t>-fx-stroke-line-cap</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -8360,27 +8360,27 @@
       <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
-          <t>.river .second</t>
+          <t>.first</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>-fx-stroke-width</t>
+          <t>-fx-stroke-line-join</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>imageMapLineShapeInnerWidth</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>imageMapLineShapeInnerWidth + "px"</t>
+          <t>"round"</t>
         </is>
       </c>
     </row>
@@ -8398,27 +8398,27 @@
       <c r="C211" t="inlineStr"/>
       <c r="D211" t="inlineStr">
         <is>
-          <t>.second</t>
+          <t>.river .second</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-stroke-width</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>imageMapLineShapeInnerWidth</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>"transparent"</t>
+          <t>imageMapLineShapeInnerWidth + "px"</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>-fx-stroke</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>-fx-stroke-line-cap</t>
+          <t>-fx-stroke</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>"round"</t>
+          <t>"transparent"</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>-fx-stroke-line-join</t>
+          <t>-fx-stroke-line-cap</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -8555,29 +8555,29 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>-fx-stroke-width</t>
+          <t>-fx-stroke-line-join</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>imageMapShapeBorderWidth</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>imageMapShapeBorderWidth + "px"</t>
+          <t>"round"</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Bild-Panel</t>
+          <t>Bild-Karte — Klickschicht</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -8588,25 +8588,29 @@
       <c r="C216" t="inlineStr"/>
       <c r="D216" t="inlineStr">
         <is>
-          <t>.my-image-background-layer</t>
+          <t>.second</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>-fx-effect</t>
+          <t>-fx-stroke-width</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>componentShadow</t>
+          <t>imageMapShapeBorderWidth</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>entfällt</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>imageMapShapeBorderWidth + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -8627,17 +8631,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-effect</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>imageLabelBgColor</t>
+          <t>componentShadow</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>vollständig durchsichtig</t>
+          <t>entfällt</t>
         </is>
       </c>
       <c r="H217" t="inlineStr"/>
@@ -8656,29 +8660,25 @@
       <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
-          <t>.my-image-border-layer</t>
+          <t>.my-image-background-layer</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>-fx-stroke</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>borderBigComponent</t>
+          <t>imageLabelBgColor</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>borderBigComponent.color()</t>
-        </is>
-      </c>
+          <t>vollständig durchsichtig</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -8699,22 +8699,22 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>-fx-stroke-type</t>
+          <t>-fx-stroke</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>borderBigComponent</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>"inside"</t>
+          <t>borderBigComponent.color()</t>
         </is>
       </c>
     </row>
@@ -8737,29 +8737,29 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>-fx-stroke-width</t>
+          <t>-fx-stroke-type</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>borderBigComponent</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>borderBigComponent.width() + "px"</t>
+          <t>"inside"</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Icon-Knopf (Zurück)</t>
+          <t>Bild-Panel</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -8770,17 +8770,17 @@
       <c r="C221" t="inlineStr"/>
       <c r="D221" t="inlineStr">
         <is>
-          <t>.my-icon-button</t>
+          <t>.my-image-border-layer</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-stroke-width</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>activeComponentBgColor</t>
+          <t>borderBigComponent</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -8788,7 +8788,11 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr"/>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>borderBigComponent.width() + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -8809,12 +8813,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>borderSmallComponent</t>
+          <t>activeComponentBgColor</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -8822,11 +8826,7 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>borderSmallComponent.width() + "px"</t>
-        </is>
-      </c>
+      <c r="H222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>-fx-background-radius</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -8862,7 +8862,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>borderSmallComponent.arc() + "px"</t>
+          <t>borderSmallComponent.width() + "px"</t>
         </is>
       </c>
     </row>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-background-radius</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>borderSmallComponent.color()</t>
+          <t>borderSmallComponent.arc() + "px"</t>
         </is>
       </c>
     </row>
@@ -8923,7 +8923,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>-fx-border-radius</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>borderSmallComponent.arc() + "px"</t>
+          <t>borderSmallComponent.color()</t>
         </is>
       </c>
     </row>
@@ -8961,7 +8961,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-border-radius</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>borderSmallComponent.width() + "px"</t>
+          <t>borderSmallComponent.arc() + "px"</t>
         </is>
       </c>
     </row>
@@ -8999,22 +8999,22 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>borderSmallComponent</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>"0"</t>
+          <t>borderSmallComponent.width() + "px"</t>
         </is>
       </c>
     </row>
@@ -9029,32 +9029,32 @@
           <t>Lernen</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>:disabled</t>
-        </is>
-      </c>
+      <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
-          <t>.my-icon-button:disabled</t>
+          <t>.my-icon-button</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>disabledComponentBgColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -9079,24 +9079,20 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>-fx-opacity</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>disabledComponentBgColor</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>"1.0"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -9111,35 +9107,39 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>:hover</t>
+          <t>:disabled</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>.my-icon-button:hover</t>
+          <t>.my-icon-button:disabled</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-opacity</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>activeComponentHoverColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H230" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>"1.0"</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Info-Feld (Frage/Fortschritt/Verlauf/Uhr)</t>
+          <t>Icon-Knopf (Zurück)</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -9147,10 +9147,14 @@
           <t>Lernen</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr"/>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>:hover</t>
+        </is>
+      </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>.my-info-label</t>
+          <t>.my-icon-button:hover</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -9160,7 +9164,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>displayTextBgColor</t>
+          <t>activeComponentHoverColor</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -9189,12 +9193,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>borderMediumComponent</t>
+          <t>displayTextBgColor</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -9202,11 +9206,7 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>border.width() + "px"</t>
-        </is>
-      </c>
+      <c r="H232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>-fx-background-radius</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>border.arc() + "px"</t>
+          <t>border.width() + "px"</t>
         </is>
       </c>
     </row>
@@ -9265,7 +9265,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-background-radius</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>border.color()</t>
+          <t>border.arc() + "px"</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9303,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>-fx-border-radius</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>border.arc() + "px"</t>
+          <t>border.color()</t>
         </is>
       </c>
     </row>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-border-radius</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -9356,7 +9356,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>border.width() + "px"</t>
+          <t>border.arc() + "px"</t>
         </is>
       </c>
     </row>
@@ -9379,20 +9379,24 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>-fx-effect</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>componentShadow</t>
+          <t>borderMediumComponent</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>entfällt</t>
-        </is>
-      </c>
-      <c r="H237" t="inlineStr"/>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>border.width() + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -9413,24 +9417,20 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-effect</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>borderMediumComponent</t>
+          <t>componentShadow</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr">
-        <is>
-          <t>padding</t>
-        </is>
-      </c>
+          <t>entfällt</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -9446,17 +9446,17 @@
       <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
-          <t>.my-info-label Text</t>
+          <t>.my-info-label</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>borderMediumComponent</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -9464,7 +9464,11 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr"/>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>padding</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -9480,22 +9484,22 @@
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
-          <t>.my-info-label.history</t>
+          <t>.my-info-label Text</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>displayTextHistoryBgColor</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>← displayTextBgColor</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H240" t="inlineStr"/>
@@ -9514,7 +9518,7 @@
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
-          <t>.my-info-label.progress</t>
+          <t>.my-info-label.history</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -9524,7 +9528,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>displayTextProgressBgColor</t>
+          <t>displayTextHistoryBgColor</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -9548,7 +9552,7 @@
       <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
-          <t>.my-info-label.question</t>
+          <t>.my-info-label.progress</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -9558,7 +9562,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>displayTextQuestionBgColor</t>
+          <t>displayTextProgressBgColor</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -9571,7 +9575,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Shape-Karte — Deko</t>
+          <t>Info-Feld (Frage/Fortschritt/Verlauf/Uhr)</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -9582,22 +9586,22 @@
       <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
-          <t>.layer-neighbor</t>
+          <t>.my-info-label.question</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>shapeMapColor0</t>
+          <t>displayTextQuestionBgColor</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>entfällt</t>
+          <t>← displayTextBgColor</t>
         </is>
       </c>
       <c r="H243" t="inlineStr"/>
@@ -9616,7 +9620,7 @@
       <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
-          <t>.layer-water</t>
+          <t>.layer-neighbor</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -9626,7 +9630,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>shapeMapColor1</t>
+          <t>shapeMapColor0</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -9639,7 +9643,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Shape-Karte — Fläche</t>
+          <t>Shape-Karte — Deko</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -9647,14 +9651,10 @@
           <t>Lernen</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>:paused, :active</t>
-        </is>
-      </c>
+      <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
-          <t>.my-shape-map-pane:paused .my-map-shape:active</t>
+          <t>.layer-water</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -9664,12 +9664,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>disabledComponentBgColor</t>
+          <t>shapeMapColor1</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>entfällt</t>
         </is>
       </c>
       <c r="H245" t="inlineStr"/>
@@ -9687,34 +9687,30 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>:paused, :active, :hover</t>
+          <t>:paused, :active</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>.my-shape-map-pane:paused .my-map-shape:active:hover</t>
+          <t>.my-shape-map-pane:paused .my-map-shape:active</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>-fx-effect</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>disabledComponentBgColor</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>"null"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -9739,25 +9735,29 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-effect</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>disabledComponentBgColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>"null"</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Shape-Karte — Form</t>
+          <t>Shape-Karte — Fläche</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -9765,25 +9765,29 @@
           <t>Lernen</t>
         </is>
       </c>
-      <c r="C248" t="inlineStr"/>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>:paused, :active, :hover</t>
+        </is>
+      </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>.my-map-shape</t>
+          <t>.my-shape-map-pane:paused .my-map-shape:active:hover</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>-fx-stroke</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>borderShapeColor</t>
+          <t>disabledComponentBgColor</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>← borderColor</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H248" t="inlineStr"/>
@@ -9807,24 +9811,20 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>-fx-stroke-width</t>
+          <t>-fx-stroke</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>shapeMapStandardBorderWidth</t>
+          <t>borderShapeColor</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>1.8 — aus der Datei nicht setzbar</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>shapeMapStandardBorderWidth + "px"</t>
-        </is>
-      </c>
+          <t>← borderColor</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -9840,27 +9840,27 @@
       <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
-          <t>.my-map-shape.layer-overlay</t>
+          <t>.my-map-shape</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-stroke-width</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>shapeMapStandardBorderWidth</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>1.8 — aus der Datei nicht setzbar</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>"transparent"</t>
+          <t>shapeMapStandardBorderWidth + "px"</t>
         </is>
       </c>
     </row>
@@ -9883,20 +9883,24 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>-fx-stroke</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>borderShapeColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>← borderColor</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>"transparent"</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -9917,24 +9921,20 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>-fx-stroke-width</t>
+          <t>-fx-stroke</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>shapeMapFederalStateBorderWidth</t>
+          <t>borderShapeColor</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>2.8 — aus der Datei nicht setzbar</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>shapeMapFederalStateBorderWidth + "px"</t>
-        </is>
-      </c>
+          <t>← borderColor</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -9947,32 +9947,32 @@
           <t>Lernen</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>:active</t>
-        </is>
-      </c>
+      <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
-          <t>.my-map-shape:active</t>
+          <t>.my-map-shape.layer-overlay</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-stroke-width</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>activeComponentBgColor</t>
+          <t>shapeMapFederalStateBorderWidth</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr"/>
+          <t>2.8 — aus der Datei nicht setzbar</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>shapeMapFederalStateBorderWidth + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -9987,34 +9987,30 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>:active, :hover</t>
+          <t>:active</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>.my-map-shape:active:hover</t>
+          <t>.my-map-shape:active</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>-fx-effect</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>activeComponentBgColor</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>"innershadow(gaussian, rgba(0,0,0,0.5), 15, 0, 0, 0)"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -10039,20 +10035,24 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-effect</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>activeComponentHoverColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>"innershadow(gaussian, rgba(0,0,0,0.5), 15, 0, 0, 0)"</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>:correct</t>
+          <t>:active, :hover</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>.my-map-shape:correct</t>
+          <t>.my-map-shape:active:hover</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>correctColor</t>
+          <t>activeComponentHoverColor</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -10105,12 +10105,12 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>:inactive</t>
+          <t>:correct</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>.my-map-shape:inactive</t>
+          <t>.my-map-shape:correct</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
@@ -10120,12 +10120,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>toEliminateColor</t>
+          <t>correctColor</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>← disabledComponentBgColor</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H257" t="inlineStr"/>
@@ -10143,12 +10143,12 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>:incorrect</t>
+          <t>:inactive</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>.my-map-shape:incorrect</t>
+          <t>.my-map-shape:inactive</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>incorrectColor</t>
+          <t>toEliminateColor</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>← disabledComponentBgColor</t>
         </is>
       </c>
       <c r="H258" t="inlineStr"/>
@@ -10181,12 +10181,12 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>:marked</t>
+          <t>:incorrect</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>.my-map-shape:marked</t>
+          <t>.my-map-shape:incorrect</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>markedColor</t>
+          <t>incorrectColor</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>(kein Zustand)</t>
+          <t>:marked</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>.my-map-shape:marked</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -10234,24 +10234,20 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>markedColor</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>keine Füllung</t>
-        </is>
-      </c>
-      <c r="H260" t="inlineStr">
-        <is>
-          <t>Formen ohne Pseudoklasse: unsichtbar und im Inneren unklickbar, siehe ShapeMapPane</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Uhr</t>
+          <t>Shape-Karte — Form</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -10259,28 +10255,36 @@
           <t>Lernen</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr"/>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>(kein Zustand)</t>
+        </is>
+      </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>.my-info-label.clock</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>displayTextClockBgColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>← displayTextBgColor</t>
-        </is>
-      </c>
-      <c r="H261" t="inlineStr"/>
+          <t>keine Füllung</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Formen ohne Pseudoklasse: unsichtbar und im Inneren unklickbar, siehe ShapeMapPane</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -10296,29 +10300,25 @@
       <c r="C262" t="inlineStr"/>
       <c r="D262" t="inlineStr">
         <is>
-          <t>.my-info-label.clock Text</t>
+          <t>.my-info-label.clock</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>-fx-font-family</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>clockFont</t>
+          <t>displayTextClockBgColor</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>← font-Familie, dreifache Größe</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>"'" + clockFont.getFamily() + "'"</t>
-        </is>
-      </c>
+          <t>← displayTextBgColor</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>-fx-font-size</t>
+          <t>-fx-font-family</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -10354,7 +10354,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>clockFont.getSize() + "px"</t>
+          <t>"'" + clockFont.getFamily() + "'"</t>
         </is>
       </c>
     </row>
@@ -10369,70 +10369,70 @@
           <t>Lernen</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>:paused</t>
-        </is>
-      </c>
+      <c r="C264" t="inlineStr"/>
       <c r="D264" t="inlineStr">
         <is>
-          <t>.my-info-label.clock:paused Text</t>
+          <t>.my-info-label.clock Text</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-font-size</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>clockPausedTextColor</t>
+          <t>clockFont</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>← textColor halb zu displayTextClockBgColor</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr"/>
+          <t>← font-Familie, dreifache Größe</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>clockFont.getSize() + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Diagramm</t>
+          <t>Uhr</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Statistik</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr"/>
+          <t>Lernen</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>:paused</t>
+        </is>
+      </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>.chart</t>
+          <t>.my-info-label.clock:paused Text</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>clockPausedTextColor</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>"transparent"</t>
-        </is>
-      </c>
+          <t>← textColor halb zu displayTextClockBgColor</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -10448,25 +10448,29 @@
       <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
-          <t>.chart .axis</t>
+          <t>.chart</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>-fx-tick-label-fill</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H266" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>"transparent"</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -10487,12 +10491,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>-fx-tick-label-font-family</t>
+          <t>-fx-tick-label-fill</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
@@ -10500,11 +10504,7 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>"'" + font.getFamily() + "'"</t>
-        </is>
-      </c>
+      <c r="H267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>-fx-tick-label-font-size</t>
+          <t>-fx-tick-label-font-family</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -10540,7 +10540,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>font.getSize() + "px"</t>
+          <t>"'" + font.getFamily() + "'"</t>
         </is>
       </c>
     </row>
@@ -10563,22 +10563,22 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>-fx-tick-label-rotation</t>
+          <t>-fx-tick-label-font-size</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>"-30"</t>
+          <t>font.getSize() + "px"</t>
         </is>
       </c>
     </row>
@@ -10596,12 +10596,12 @@
       <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
-          <t>.chart .axis .axis-minor-tick-mark</t>
+          <t>.chart .axis</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>-fx-stroke</t>
+          <t>-fx-tick-label-rotation</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -10616,7 +10616,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>"transparent"</t>
+          <t>"-30"</t>
         </is>
       </c>
     </row>
@@ -10639,7 +10639,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>-fx-stroke-width</t>
+          <t>-fx-stroke</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>"0px"</t>
+          <t>"transparent"</t>
         </is>
       </c>
     </row>
@@ -10672,27 +10672,27 @@
       <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
-          <t>.chart .axis-label</t>
+          <t>.chart .axis .axis-minor-tick-mark</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>-fx-font-family</t>
+          <t>-fx-stroke-width</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>"'" + font.getFamily() + "'"</t>
+          <t>"0px"</t>
         </is>
       </c>
     </row>
@@ -10715,7 +10715,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>-fx-font-size</t>
+          <t>-fx-font-family</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>font.getSize() + "px"</t>
+          <t>"'" + font.getFamily() + "'"</t>
         </is>
       </c>
     </row>
@@ -10753,12 +10753,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>-fx-text-fill</t>
+          <t>-fx-font-size</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
@@ -10766,7 +10766,11 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H274" t="inlineStr"/>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>font.getSize() + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -10782,12 +10786,12 @@
       <c r="C275" t="inlineStr"/>
       <c r="D275" t="inlineStr">
         <is>
-          <t>.chart .axis:bottom</t>
+          <t>.chart .axis-label</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-text-fill</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -10800,11 +10804,7 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>UiUtils.toHex(textColor) + " transparent transparent transparent"</t>
-        </is>
-      </c>
+      <c r="H275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -10820,27 +10820,27 @@
       <c r="C276" t="inlineStr"/>
       <c r="D276" t="inlineStr">
         <is>
-          <t>.chart .axis:bottom .axis-tick-mark</t>
+          <t>.chart .axis:bottom</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>-fx-stroke</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>"transparent"</t>
+          <t>UiUtils.toHex(textColor) + " transparent transparent transparent"</t>
         </is>
       </c>
     </row>
@@ -10863,7 +10863,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>-fx-stroke-width</t>
+          <t>-fx-stroke</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -10878,7 +10878,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>"0px"</t>
+          <t>"transparent"</t>
         </is>
       </c>
     </row>
@@ -10896,27 +10896,27 @@
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
-          <t>.chart .axis:left</t>
+          <t>.chart .axis:bottom .axis-tick-mark</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-stroke-width</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>"transparent " + UiUtils.toHex(textColor) + " transparent transparent"</t>
+          <t>"0px"</t>
         </is>
       </c>
     </row>
@@ -10934,12 +10934,12 @@
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
-          <t>.chart .axis:left .axis-tick-mark</t>
+          <t>.chart .axis:left</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>-fx-stroke</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -10952,7 +10952,11 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H279" t="inlineStr"/>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>"transparent " + UiUtils.toHex(textColor) + " transparent transparent"</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -10973,24 +10977,20 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>-fx-stroke-width</t>
+          <t>-fx-stroke</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>"1px"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -11006,12 +11006,12 @@
       <c r="C281" t="inlineStr"/>
       <c r="D281" t="inlineStr">
         <is>
-          <t>.chart-container</t>
+          <t>.chart .axis:left .axis-tick-mark</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>-fx-spacing</t>
+          <t>-fx-stroke-width</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>"20px"</t>
+          <t>"1px"</t>
         </is>
       </c>
     </row>
@@ -11044,12 +11044,12 @@
       <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
-          <t>.chart-content</t>
+          <t>.chart-container</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-spacing</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>"transparent"</t>
+          <t>"20px"</t>
         </is>
       </c>
     </row>
@@ -11082,12 +11082,12 @@
       <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
-          <t>.chart-controls</t>
+          <t>.chart-content</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>-fx-alignment</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>"center-left"</t>
+          <t>"transparent"</t>
         </is>
       </c>
     </row>
@@ -11125,22 +11125,22 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>-fx-spacing</t>
+          <t>-fx-alignment</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>spacing + "px"</t>
+          <t>"center-left"</t>
         </is>
       </c>
     </row>
@@ -11158,27 +11158,27 @@
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
-          <t>.chart-plot-background</t>
+          <t>.chart-controls</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-spacing</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>"transparent"</t>
+          <t>spacing + "px"</t>
         </is>
       </c>
     </row>
@@ -11196,25 +11196,29 @@
       <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>.chart-root</t>
+          <t>.chart-plot-background</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>chartRootPadding</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>"50px 50px 50px 50px"</t>
-        </is>
-      </c>
-      <c r="H286" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>"transparent"</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -11230,22 +11234,22 @@
       <c r="C287" t="inlineStr"/>
       <c r="D287" t="inlineStr">
         <is>
-          <t>.chart-series-line</t>
+          <t>.chart-root</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>-fx-stroke</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>chartRootPadding</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>"50px 50px 50px 50px"</t>
         </is>
       </c>
       <c r="H287" t="inlineStr"/>
@@ -11269,29 +11273,25 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>-fx-stroke-width</t>
+          <t>-fx-stroke</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H288" t="inlineStr">
-        <is>
-          <t>"1px"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Diagramm — Balken</t>
+          <t>Diagramm</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -11302,25 +11302,29 @@
       <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
-          <t>.chart-bar</t>
+          <t>.chart-series-line</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-stroke-width</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H289" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>"1px"</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -11341,24 +11345,20 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H290" t="inlineStr">
-        <is>
-          <t>"1px"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -11371,32 +11371,32 @@
           <t>Statistik</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr">
-        <is>
-          <t>:achieved</t>
-        </is>
-      </c>
+      <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
-          <t>.chart-bar:achieved</t>
+          <t>.chart-bar</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>-fx-bar-fill</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>correctColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H291" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>"1px"</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -11411,12 +11411,12 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>:failed</t>
+          <t>:achieved</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>.chart-bar:failed</t>
+          <t>.chart-bar:achieved</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>incorrectColor</t>
+          <t>correctColor</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
@@ -11449,12 +11449,12 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>:in-progress</t>
+          <t>:failed</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>.chart-bar:in-progress</t>
+          <t>.chart-bar:failed</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>markedColor</t>
+          <t>incorrectColor</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
@@ -11477,7 +11477,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Tabelle</t>
+          <t>Diagramm — Balken</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -11485,32 +11485,32 @@
           <t>Statistik</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr"/>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>:in-progress</t>
+        </is>
+      </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>.my-table-view</t>
+          <t>.chart-bar:in-progress</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-bar-fill</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>markedColor</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H294" t="inlineStr">
-        <is>
-          <t>"0"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -11531,20 +11531,24 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H295" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -11565,24 +11569,20 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>"1"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -11603,20 +11603,24 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>-fx-effect</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>componentShadow</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>entfällt</t>
-        </is>
-      </c>
-      <c r="H297" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>"1"</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -11637,24 +11641,20 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>-fx-faint-focus-color</t>
+          <t>-fx-effect</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>componentShadow</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H298" t="inlineStr">
-        <is>
-          <t>"transparent"</t>
-        </is>
-      </c>
+          <t>entfällt</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -11675,7 +11675,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>-fx-focus-color</t>
+          <t>-fx-faint-focus-color</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -11713,7 +11713,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-focus-color</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>"0"</t>
+          <t>"transparent"</t>
         </is>
       </c>
     </row>
@@ -11746,12 +11746,12 @@
       <c r="C301" t="inlineStr"/>
       <c r="D301" t="inlineStr">
         <is>
-          <t>.my-table-view .column-header .label</t>
+          <t>.my-table-view</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>-fx-alignment</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -11766,7 +11766,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>"CENTER-LEFT"</t>
+          <t>"0"</t>
         </is>
       </c>
     </row>
@@ -11784,25 +11784,29 @@
       <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
-          <t>.my-table-view .column-header, .my-table-view .filler</t>
+          <t>.my-table-view .column-header .label</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-alignment</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>menuBarBackground</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H302" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>"CENTER-LEFT"</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -11823,12 +11827,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>menuBarBackground</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -11836,11 +11840,7 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H303" t="inlineStr">
-        <is>
-          <t>"transparent " + UiUtils.toHex(textColor) + " " + UiUtils.toHex(textColor) + " transparent</t>
-        </is>
-      </c>
+      <c r="H303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -11856,25 +11856,29 @@
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
-          <t>.my-table-view .column-header-background</t>
+          <t>.my-table-view .column-header, .my-table-view .filler</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>playFieldBackground</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>← menuBarBackground</t>
-        </is>
-      </c>
-      <c r="H304" t="inlineStr"/>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>"transparent " + UiUtils.toHex(textColor) + " " + UiUtils.toHex(textColor) + " transparent</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -11890,29 +11894,25 @@
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>.my-table-view .table-cell</t>
+          <t>.my-table-view .column-header-background</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>playFieldBackground</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H305" t="inlineStr">
-        <is>
-          <t>"transparent " + UiUtils.toHex(textColor) + " transparent transparent"</t>
-        </is>
-      </c>
+          <t>← menuBarBackground</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -11928,27 +11928,27 @@
       <c r="C306" t="inlineStr"/>
       <c r="D306" t="inlineStr">
         <is>
-          <t>.my-table-view .table-row-cell</t>
+          <t>.my-table-view .table-cell</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>playFieldBackground</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>← menuBarBackground</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>UiUtils.toHex(textColor) + ", " + UiUtils.toHex(UiUtils.contrastingShade(playFieldBackgrou</t>
+          <t>"transparent " + UiUtils.toHex(textColor) + " transparent transparent"</t>
         </is>
       </c>
     </row>
@@ -11976,12 +11976,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>playFieldBackground</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>← menuBarBackground</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -12001,34 +12001,30 @@
           <t>Statistik</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr">
-        <is>
-          <t>:focused</t>
-        </is>
-      </c>
+      <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
-          <t>.my-table-view .table-row-cell:focused</t>
+          <t>.my-table-view .table-row-cell</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>"0, 0 0 1 0"</t>
+          <t>UiUtils.toHex(textColor) + ", " + UiUtils.toHex(UiUtils.contrastingShade(playFieldBackgrou</t>
         </is>
       </c>
     </row>
@@ -12045,32 +12041,32 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>:odd</t>
+          <t>:focused</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>.my-table-view .table-row-cell:odd</t>
+          <t>.my-table-view .table-row-cell:focused</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>playFieldBackground</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>← menuBarBackground</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>UiUtils.toHex(textColor) + ", " + UiUtils.toHex(playFieldBackground)</t>
+          <t>"0, 0 0 1 0"</t>
         </is>
       </c>
     </row>
@@ -12102,12 +12098,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>playFieldBackground</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>← menuBarBackground</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -12129,12 +12125,12 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>:selected</t>
+          <t>:odd</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>.my-table-view .table-row-cell:selected</t>
+          <t>.my-table-view .table-row-cell:odd</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
@@ -12144,17 +12140,17 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>menuBarHoverBackground</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>← contrastingShade(menuBarBackground, 20)</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>UiUtils.toHex(textColor) + ", " + UiUtils.toHex(menuBarHoverBackground)</t>
+          <t>UiUtils.toHex(textColor) + ", " + UiUtils.toHex(playFieldBackground)</t>
         </is>
       </c>
     </row>
@@ -12186,12 +12182,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>menuBarHoverBackground</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>← contrastingShade(menuBarBackground, 20)</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -12223,22 +12219,22 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>"0, 0 0 1 0"</t>
+          <t>UiUtils.toHex(textColor) + ", " + UiUtils.toHex(menuBarHoverBackground)</t>
         </is>
       </c>
     </row>
@@ -12253,10 +12249,14 @@
           <t>Statistik</t>
         </is>
       </c>
-      <c r="C314" t="inlineStr"/>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>:selected</t>
+        </is>
+      </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>.my-table-view .text-field</t>
+          <t>.my-table-view .table-row-cell:selected</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>"0"</t>
+          <t>"0, 0 0 1 0"</t>
         </is>
       </c>
     </row>
@@ -12299,7 +12299,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -12367,19 +12367,15 @@
           <t>Statistik</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr">
-        <is>
-          <t>:focused</t>
-        </is>
-      </c>
+      <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
-          <t>.my-table-view .text-field:focused</t>
+          <t>.my-table-view .text-field</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -12421,7 +12417,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -12458,12 +12454,12 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>.my-table-view:focused</t>
+          <t>.my-table-view .text-field:focused</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -12478,7 +12474,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>"-fx-control-inner-background"</t>
+          <t>"0"</t>
         </is>
       </c>
     </row>
@@ -12505,7 +12501,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -12520,7 +12516,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>"0"</t>
+          <t>"-fx-control-inner-background"</t>
         </is>
       </c>
     </row>
@@ -12547,7 +12543,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -12569,36 +12565,44 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Schlagwort — Löschknopf</t>
+          <t>Tabelle</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Tagebuch</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr"/>
+          <t>Statistik</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>:focused</t>
+        </is>
+      </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>.tag-chip-remove</t>
+          <t>.my-table-view:focused</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>playFieldBackground</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>← menuBarBackground</t>
-        </is>
-      </c>
-      <c r="H322" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -12619,24 +12623,20 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>playFieldBackground</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t>Color.TRANSPARENT</t>
-        </is>
-      </c>
+          <t>← menuBarBackground</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -12657,7 +12657,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -12672,7 +12672,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>"0px"</t>
+          <t>Color.TRANSPARENT</t>
         </is>
       </c>
     </row>
@@ -12695,7 +12695,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -12710,7 +12710,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>"0 0"</t>
+          <t>"0px"</t>
         </is>
       </c>
     </row>
@@ -12728,30 +12728,34 @@
       <c r="C326" t="inlineStr"/>
       <c r="D326" t="inlineStr">
         <is>
-          <t>.tag-chip-remove .text</t>
+          <t>.tag-chip-remove</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H326" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>"0 0"</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Tagebuch — Layout</t>
+          <t>Schlagwort — Löschknopf</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -12762,29 +12766,25 @@
       <c r="C327" t="inlineStr"/>
       <c r="D327" t="inlineStr">
         <is>
-          <t>.diary-viewer-filter-bar</t>
+          <t>.tag-chip-remove .text</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>-fx-max-width</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>diaryViewerContentPercent</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>63 — Prozent der contentSize, nur Obergrenze</t>
-        </is>
-      </c>
-      <c r="H327" t="inlineStr">
-        <is>
-          <t>spaltenBreite + "px"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>contentSize</t>
+          <t>diaryViewerContentPercent</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>1910 × 1000 — aus der Datei nicht setzbar</t>
+          <t>63 — Prozent der contentSize, nur Obergrenze</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -12843,22 +12843,22 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>-fx-spacing</t>
+          <t>-fx-max-width</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>contentSize</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>1910 × 1000 — aus der Datei nicht setzbar</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>font.getSize() * 0.5 + "px"</t>
+          <t>spaltenBreite + "px"</t>
         </is>
       </c>
     </row>
@@ -12876,17 +12876,17 @@
       <c r="C330" t="inlineStr"/>
       <c r="D330" t="inlineStr">
         <is>
-          <t>.diary-viewer-hint</t>
+          <t>.diary-viewer-filter-bar</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>incorrectTextColor</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
@@ -12894,7 +12894,11 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H330" t="inlineStr"/>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>"0px 0px 0px " + (scrollPolster + schatten.left()) + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -12910,27 +12914,27 @@
       <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
-          <t>.diary-viewer-hint</t>
+          <t>.diary-viewer-filter-bar</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>-fx-font-style</t>
+          <t>-fx-spacing</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>"italic"</t>
+          <t>scrollPolster + "px"</t>
         </is>
       </c>
     </row>
@@ -12948,17 +12952,17 @@
       <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
-          <t>.diary-viewer-results</t>
+          <t>.diary-viewer-hint</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>incorrectTextColor</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
@@ -12966,11 +12970,7 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H332" t="inlineStr">
-        <is>
-          <t>font.getSize() + "px 0px"</t>
-        </is>
-      </c>
+      <c r="H332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -12986,27 +12986,27 @@
       <c r="C333" t="inlineStr"/>
       <c r="D333" t="inlineStr">
         <is>
-          <t>.diary-viewer-results</t>
+          <t>.diary-viewer-hint</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>-fx-spacing</t>
+          <t>-fx-font-style</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>font.getSize() + "px"</t>
+          <t>"italic"</t>
         </is>
       </c>
     </row>
@@ -13024,7 +13024,7 @@
       <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr">
         <is>
-          <t>.diary-viewer-root</t>
+          <t>.diary-viewer-results</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -13044,7 +13044,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>font.getSize() + "px 0px"</t>
+          <t>innenabstand(Math.max(font.getSize(), schatten.top()), schatten.right(), Math.max(font.get</t>
         </is>
       </c>
     </row>
@@ -13062,7 +13062,7 @@
       <c r="C335" t="inlineStr"/>
       <c r="D335" t="inlineStr">
         <is>
-          <t>.diary-viewer-root</t>
+          <t>.diary-viewer-results</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -13082,7 +13082,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>font.getSize() * 0.5 + "px"</t>
+          <t>Math.max(font.getSize(), schatten.bottom()) + "px"</t>
         </is>
       </c>
     </row>
@@ -13100,27 +13100,27 @@
       <c r="C336" t="inlineStr"/>
       <c r="D336" t="inlineStr">
         <is>
-          <t>.diary-viewer-scroll</t>
+          <t>.diary-viewer-root</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>-fx-background</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>"transparent"</t>
+          <t>font.getSize() + "px 0px"</t>
         </is>
       </c>
     </row>
@@ -13138,27 +13138,27 @@
       <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
-          <t>.diary-viewer-scroll</t>
+          <t>.diary-viewer-root</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-spacing</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>"transparent"</t>
+          <t>font.getSize() * 0.5 + "px"</t>
         </is>
       </c>
     </row>
@@ -13181,22 +13181,22 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>-fx-max-width</t>
+          <t>-fx-background</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>diaryViewerContentPercent</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>63 — Prozent der contentSize, nur Obergrenze</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>spaltenBreite + "px"</t>
+          <t>"transparent"</t>
         </is>
       </c>
     </row>
@@ -13219,22 +13219,22 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>-fx-max-width</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>contentSize</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>1910 × 1000 — aus der Datei nicht setzbar</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>spaltenBreite + "px"</t>
+          <t>"transparent"</t>
         </is>
       </c>
     </row>
@@ -13257,22 +13257,22 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-max-width</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>diaryViewerContentPercent</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>63 — Prozent der contentSize, nur Obergrenze</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>font.getSize() * 0.5 + "px"</t>
+          <t>spaltenBreite + "px"</t>
         </is>
       </c>
     </row>
@@ -13290,34 +13290,34 @@
       <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
         <is>
-          <t>.diary-viewer-scroll .viewport</t>
+          <t>.diary-viewer-scroll</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-max-width</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>contentSize</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>1910 × 1000 — aus der Datei nicht setzbar</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>"transparent"</t>
+          <t>spaltenBreite + "px"</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Tagebuchkarte</t>
+          <t>Tagebuch — Layout</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -13328,30 +13328,34 @@
       <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
-          <t>.diary-card</t>
+          <t>.diary-viewer-scroll</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>displayTextQuestionBgColor</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>← displayTextBgColor</t>
-        </is>
-      </c>
-      <c r="H342" t="inlineStr"/>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>scrollPolster + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Tagebuchkarte</t>
+          <t>Tagebuch — Layout</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -13362,27 +13366,27 @@
       <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
-          <t>.diary-card</t>
+          <t>.diary-viewer-scroll .viewport</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>borderBigComponent</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>borderBigComponent.width() + "px"</t>
+          <t>"transparent"</t>
         </is>
       </c>
     </row>
@@ -13405,24 +13409,20 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>-fx-background-radius</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>borderBigComponent</t>
+          <t>displayTextQuestionBgColor</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H344" t="inlineStr">
-        <is>
-          <t>borderBigComponent.arc() + "px"</t>
-        </is>
-      </c>
+          <t>← displayTextBgColor</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>borderBigComponent.color()</t>
+          <t>borderBigComponent.width() + "px"</t>
         </is>
       </c>
     </row>
@@ -13481,7 +13481,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>-fx-border-radius</t>
+          <t>-fx-background-radius</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -13519,7 +13519,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>borderBigComponent.width() + "px"</t>
+          <t>borderBigComponent.color()</t>
         </is>
       </c>
     </row>
@@ -13557,22 +13557,22 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>-fx-cursor</t>
+          <t>-fx-border-radius</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>borderBigComponent</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>"hand"</t>
+          <t>borderBigComponent.arc() + "px"</t>
         </is>
       </c>
     </row>
@@ -13595,20 +13595,24 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>-fx-effect</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>componentShadow</t>
+          <t>borderBigComponent</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>entfällt</t>
-        </is>
-      </c>
-      <c r="H349" t="inlineStr"/>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>borderBigComponent.width() + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -13629,22 +13633,22 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-cursor</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>font.getSize() + "px"</t>
+          <t>"hand"</t>
         </is>
       </c>
     </row>
@@ -13662,22 +13666,22 @@
       <c r="C351" t="inlineStr"/>
       <c r="D351" t="inlineStr">
         <is>
-          <t>.diary-card-date</t>
+          <t>.diary-card</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-effect</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>componentShadow</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>entfällt</t>
         </is>
       </c>
       <c r="H351" t="inlineStr"/>
@@ -13696,27 +13700,27 @@
       <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
         <is>
-          <t>.diary-card-date</t>
+          <t>.diary-card</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>-fx-font-weight</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>"bold"</t>
+          <t>font.getSize() + "px"</t>
         </is>
       </c>
     </row>
@@ -13734,7 +13738,7 @@
       <c r="C353" t="inlineStr"/>
       <c r="D353" t="inlineStr">
         <is>
-          <t>.diary-card-tags</t>
+          <t>.diary-card-date</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -13768,12 +13772,12 @@
       <c r="C354" t="inlineStr"/>
       <c r="D354" t="inlineStr">
         <is>
-          <t>.diary-card-tags</t>
+          <t>.diary-card-date</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>-fx-font-style</t>
+          <t>-fx-font-weight</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -13788,7 +13792,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>"italic"</t>
+          <t>"bold"</t>
         </is>
       </c>
     </row>
@@ -13806,7 +13810,7 @@
       <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr">
         <is>
-          <t>.diary-card-text</t>
+          <t>.diary-card-tags</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -13837,37 +13841,37 @@
           <t>Tagebuch</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>:hover</t>
-        </is>
-      </c>
+      <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
-          <t>.diary-card:hover</t>
+          <t>.diary-card-tags</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-font-style</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>displayTextQuestionBgColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>← displayTextBgColor</t>
-        </is>
-      </c>
-      <c r="H356" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>"italic"</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Vorschlagsliste</t>
+          <t>Tagebuchkarte</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -13878,17 +13882,17 @@
       <c r="C357" t="inlineStr"/>
       <c r="D357" t="inlineStr">
         <is>
-          <t>.suggestion-box</t>
+          <t>.diary-card-text</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>menuBarBackground</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
@@ -13901,7 +13905,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Vorschlagsliste</t>
+          <t>Tagebuchkarte</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -13909,25 +13913,29 @@
           <t>Tagebuch</t>
         </is>
       </c>
-      <c r="C358" t="inlineStr"/>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>:hover</t>
+        </is>
+      </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>.suggestion-box</t>
+          <t>.diary-card:hover</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>borderColor</t>
+          <t>displayTextQuestionBgColor</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>← displayTextBgColor</t>
         </is>
       </c>
       <c r="H358" t="inlineStr"/>
@@ -13951,24 +13959,20 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>menuBarBackground</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H359" t="inlineStr">
-        <is>
-          <t>"1px"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -13984,29 +13988,25 @@
       <c r="C360" t="inlineStr"/>
       <c r="D360" t="inlineStr">
         <is>
-          <t>.suggestion-box .label</t>
+          <t>.suggestion-box</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>borderColor</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H360" t="inlineStr">
-        <is>
-          <t>"5 5"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -14019,113 +14019,113 @@
           <t>Tagebuch</t>
         </is>
       </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>:highlighted</t>
-        </is>
-      </c>
+      <c r="C361" t="inlineStr"/>
       <c r="D361" t="inlineStr">
         <is>
-          <t>.suggestion-box :highlighted</t>
+          <t>.suggestion-box</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>menuBarHoverBackground</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>← contrastingShade(menuBarBackground, 20)</t>
-        </is>
-      </c>
-      <c r="H361" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>"1px"</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Alles (Wurzel)</t>
+          <t>Vorschlagsliste</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>überall</t>
+          <t>Tagebuch</t>
         </is>
       </c>
       <c r="C362" t="inlineStr"/>
       <c r="D362" t="inlineStr">
         <is>
-          <t>.root</t>
+          <t>.suggestion-box .label</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>-fx-font-family</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>"'" + font.getFamily() + "'"</t>
+          <t>"5 5"</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Alles (Wurzel)</t>
+          <t>Vorschlagsliste</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>überall</t>
-        </is>
-      </c>
-      <c r="C363" t="inlineStr"/>
+          <t>Tagebuch</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>:highlighted</t>
+        </is>
+      </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>.root</t>
+          <t>.suggestion-box :highlighted</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>-fx-font-size</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>menuBarHoverBackground</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H363" t="inlineStr">
-        <is>
-          <t>font.getSize() + "px"</t>
-        </is>
-      </c>
+          <t>← contrastingShade(menuBarBackground, 20)</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Bildlaufleiste</t>
+          <t>Alles (Wurzel)</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -14136,17 +14136,17 @@
       <c r="C364" t="inlineStr"/>
       <c r="D364" t="inlineStr">
         <is>
-          <t>.scroll-bar .increment-arrow, .scroll-bar .decrement-arrow</t>
+          <t>.root</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-font-family</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
@@ -14154,12 +14154,16 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H364" t="inlineStr"/>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>"'" + font.getFamily() + "'"</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Bildlaufleiste</t>
+          <t>Alles (Wurzel)</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -14170,17 +14174,17 @@
       <c r="C365" t="inlineStr"/>
       <c r="D365" t="inlineStr">
         <is>
-          <t>.scroll-bar .increment-button, .scroll-bar .decrement-button</t>
+          <t>.root</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-font-size</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>menuBarBackground</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
@@ -14188,7 +14192,11 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H365" t="inlineStr"/>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>font.getSize() + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -14204,7 +14212,7 @@
       <c r="C366" t="inlineStr"/>
       <c r="D366" t="inlineStr">
         <is>
-          <t>.scroll-bar .thumb</t>
+          <t>.scroll-bar .increment-arrow, .scroll-bar .decrement-arrow</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -14214,7 +14222,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>activeComponentBgColor</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
@@ -14235,14 +14243,10 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C367" t="inlineStr">
-        <is>
-          <t>:hover</t>
-        </is>
-      </c>
+      <c r="C367" t="inlineStr"/>
       <c r="D367" t="inlineStr">
         <is>
-          <t>.scroll-bar .thumb:hover</t>
+          <t>.scroll-bar .increment-button, .scroll-bar .decrement-button</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -14252,7 +14256,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>activeComponentHoverColor</t>
+          <t>menuBarBackground</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
@@ -14276,7 +14280,7 @@
       <c r="C368" t="inlineStr"/>
       <c r="D368" t="inlineStr">
         <is>
-          <t>.scroll-bar .track</t>
+          <t>.scroll-bar .thumb</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -14286,24 +14290,20 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>playFieldBackground</t>
+          <t>activeComponentBgColor</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>← menuBarBackground</t>
-        </is>
-      </c>
-      <c r="H368" t="inlineStr">
-        <is>
-          <t>UiUtils.contrastingShade(playFieldBackground,10)</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Eingabefeld</t>
+          <t>Bildlaufleiste</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -14311,37 +14311,37 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C369" t="inlineStr"/>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>:hover</t>
+        </is>
+      </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>.text-field</t>
+          <t>.scroll-bar .thumb:hover</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>-fx-alignment</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>activeComponentHoverColor</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H369" t="inlineStr">
-        <is>
-          <t>"center"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Eingabefeld</t>
+          <t>Bildlaufleiste</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -14352,7 +14352,7 @@
       <c r="C370" t="inlineStr"/>
       <c r="D370" t="inlineStr">
         <is>
-          <t>.text-field</t>
+          <t>.scroll-bar .track</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -14362,15 +14362,19 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>activeComponentBgColor</t>
+          <t>playFieldBackground</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H370" t="inlineStr"/>
+          <t>← menuBarBackground</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>UiUtils.contrastingShade(playFieldBackground,10)</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -14391,22 +14395,22 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-alignment</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>borderSmallComponent</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>fest im Code</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>borderSmallComponent.width() + "px"</t>
+          <t>"center"</t>
         </is>
       </c>
     </row>
@@ -14429,12 +14433,12 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>-fx-background-radius</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>borderSmallComponent</t>
+          <t>activeComponentBgColor</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
@@ -14442,11 +14446,7 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H372" t="inlineStr">
-        <is>
-          <t>borderSmallComponent.arc() + "px"</t>
-        </is>
-      </c>
+      <c r="H372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -14467,7 +14467,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -14482,7 +14482,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>borderSmallComponent.color()</t>
+          <t>borderSmallComponent.width() + "px"</t>
         </is>
       </c>
     </row>
@@ -14505,7 +14505,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>-fx-border-radius</t>
+          <t>-fx-background-radius</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -14558,7 +14558,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>borderSmallComponent.width() + "px"</t>
+          <t>borderSmallComponent.color()</t>
         </is>
       </c>
     </row>
@@ -14581,20 +14581,24 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>-fx-effect</t>
+          <t>-fx-border-radius</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>componentShadow</t>
+          <t>borderSmallComponent</t>
         </is>
       </c>
       <c r="G376" t="inlineStr">
         <is>
-          <t>entfällt</t>
-        </is>
-      </c>
-      <c r="H376" t="inlineStr"/>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>borderSmallComponent.arc() + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -14615,7 +14619,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -14630,7 +14634,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>paddingCss</t>
+          <t>borderSmallComponent.width() + "px"</t>
         </is>
       </c>
     </row>
@@ -14653,17 +14657,17 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>-fx-text-fill</t>
+          <t>-fx-effect</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>textActiveComponentColor</t>
+          <t>componentShadow</t>
         </is>
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>← textColor</t>
+          <t>entfällt</t>
         </is>
       </c>
       <c r="H378" t="inlineStr"/>
@@ -14679,24 +14683,20 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C379" t="inlineStr">
-        <is>
-          <t>:disabled</t>
-        </is>
-      </c>
+      <c r="C379" t="inlineStr"/>
       <c r="D379" t="inlineStr">
         <is>
-          <t>.text-field:disabled</t>
+          <t>.text-field</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>disabledComponentBgColor</t>
+          <t>borderSmallComponent</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
@@ -14704,7 +14704,11 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H379" t="inlineStr"/>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>paddingCss</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -14717,36 +14721,28 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C380" t="inlineStr">
-        <is>
-          <t>:disabled</t>
-        </is>
-      </c>
+      <c r="C380" t="inlineStr"/>
       <c r="D380" t="inlineStr">
         <is>
-          <t>.text-field:disabled</t>
+          <t>.text-field</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-text-fill</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>borderSmallComponent</t>
+          <t>textActiveComponentColor</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H380" t="inlineStr">
-        <is>
-          <t>borderSmallComponent.disabledColor()</t>
-        </is>
-      </c>
+          <t>← textColor</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -14771,24 +14767,20 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>-fx-font-weight</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>disabledComponentBgColor</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H381" t="inlineStr">
-        <is>
-          <t>"bold"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -14813,22 +14805,22 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>-fx-opacity</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>borderSmallComponent</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>fest im Code</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>"1.0"</t>
+          <t>borderSmallComponent.disabledColor()</t>
         </is>
       </c>
     </row>
@@ -14855,20 +14847,24 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>-fx-text-fill</t>
+          <t>-fx-font-weight</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>incorrectTextColor</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H383" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>"bold"</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -14883,30 +14879,34 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>:focused</t>
+          <t>:disabled</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>.text-field:focused</t>
+          <t>.text-field:disabled</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-opacity</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>activeBorderWidth</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H384" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>"1.0"</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -14921,27 +14921,27 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>:focused</t>
+          <t>:disabled</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>.text-field:focused</t>
+          <t>.text-field:disabled</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-text-fill</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>activeBorderColor</t>
+          <t>incorrectTextColor</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>entfällt</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H385" t="inlineStr"/>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
@@ -14997,27 +14997,27 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>:invalid-query</t>
+          <t>:focused</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>.text-field:invalid-query</t>
+          <t>.text-field:focused</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>-fx-text-fill</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>incorrectTextColor</t>
+          <t>activeBorderColor</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>entfällt</t>
         </is>
       </c>
       <c r="H387" t="inlineStr"/>
@@ -15025,7 +15025,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Jeder Text</t>
+          <t>Eingabefeld</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -15033,25 +15033,29 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C388" t="inlineStr"/>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>:focused</t>
+        </is>
+      </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>.text</t>
+          <t>.text-field:focused</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>activeBorderWidth</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>Pflicht</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H388" t="inlineStr"/>
@@ -15059,7 +15063,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Knopf</t>
+          <t>Eingabefeld</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -15067,25 +15071,29 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C389" t="inlineStr"/>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>:invalid-query</t>
+        </is>
+      </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>.button .text, .date-picker .arrow-button .text</t>
+          <t>.text-field:invalid-query</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>-fx-fill</t>
+          <t>-fx-text-fill</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>textActiveComponentColor</t>
+          <t>incorrectTextColor</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>← textColor</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H389" t="inlineStr"/>
@@ -15093,7 +15101,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Knopf</t>
+          <t>Jeder Text</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -15104,17 +15112,17 @@
       <c r="C390" t="inlineStr"/>
       <c r="D390" t="inlineStr">
         <is>
-          <t>.button, .date-picker .arrow-button, .spinner .increment-arrow-button, .spinner .decrement-arrow-button</t>
+          <t>.text</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>activeComponentBgColor</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
@@ -15138,29 +15146,25 @@
       <c r="C391" t="inlineStr"/>
       <c r="D391" t="inlineStr">
         <is>
-          <t>.button, .date-picker .arrow-button, .spinner .increment-arrow-button, .spinner .decrement-arrow-button</t>
+          <t>.button .text, .date-picker .arrow-button .text</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>-fx-background-insets</t>
+          <t>-fx-fill</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>borderSmallComponent</t>
+          <t>textActiveComponentColor</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H391" t="inlineStr">
-        <is>
-          <t>borderSmallComponent.width() + "px"</t>
-        </is>
-      </c>
+          <t>← textColor</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -15181,12 +15185,12 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>-fx-background-radius</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>borderSmallComponent</t>
+          <t>activeComponentBgColor</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
@@ -15194,11 +15198,7 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H392" t="inlineStr">
-        <is>
-          <t>borderSmallComponent.arc() + "px"</t>
-        </is>
-      </c>
+      <c r="H392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-background-insets</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -15234,7 +15234,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>borderSmallComponent.color()</t>
+          <t>borderSmallComponent.width() + "px"</t>
         </is>
       </c>
     </row>
@@ -15257,7 +15257,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>-fx-border-radius</t>
+          <t>-fx-background-radius</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
@@ -15295,7 +15295,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -15310,7 +15310,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>borderSmallComponent.width() + "px"</t>
+          <t>borderSmallComponent.color()</t>
         </is>
       </c>
     </row>
@@ -15333,20 +15333,24 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>-fx-effect</t>
+          <t>-fx-border-radius</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>componentShadow</t>
+          <t>borderSmallComponent</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>entfällt</t>
-        </is>
-      </c>
-      <c r="H396" t="inlineStr"/>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>borderSmallComponent.arc() + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -15359,24 +15363,20 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C397" t="inlineStr">
-        <is>
-          <t>:hover, :hover</t>
-        </is>
-      </c>
+      <c r="C397" t="inlineStr"/>
       <c r="D397" t="inlineStr">
         <is>
-          <t>.button:hover, .date-picker .arrow-button:hover</t>
+          <t>.button, .date-picker .arrow-button, .spinner .increment-arrow-button, .spinner .decrement-arrow-button</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>activeComponentHoverColor</t>
+          <t>borderSmallComponent</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
@@ -15384,7 +15384,11 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H397" t="inlineStr"/>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>borderSmallComponent.width() + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -15397,41 +15401,33 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>:pressed, :pressed</t>
-        </is>
-      </c>
+      <c r="C398" t="inlineStr"/>
       <c r="D398" t="inlineStr">
         <is>
-          <t>.button:pressed, .date-picker .arrow-button:pressed</t>
+          <t>.button, .date-picker .arrow-button, .spinner .increment-arrow-button, .spinner .decrement-arrow-button</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-effect</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>activeComponentHoverColor</t>
+          <t>componentShadow</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H398" t="inlineStr">
-        <is>
-          <t>UiUtils.contrastingShade(activeComponentHoverColor, 8)</t>
-        </is>
-      </c>
+          <t>entfällt</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Menü</t>
+          <t>Knopf</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -15439,10 +15435,14 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C399" t="inlineStr"/>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>:hover, :hover</t>
+        </is>
+      </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>.context-menu</t>
+          <t>.button:hover, .date-picker .arrow-button:hover</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -15452,7 +15452,7 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>menuBarBackground</t>
+          <t>activeComponentHoverColor</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
@@ -15465,7 +15465,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Menü</t>
+          <t>Knopf</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -15473,20 +15473,24 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C400" t="inlineStr"/>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>:pressed, :pressed</t>
+        </is>
+      </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>.context-menu</t>
+          <t>.button:pressed, .date-picker .arrow-button:pressed</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>thinBorderColor</t>
+          <t>activeComponentHoverColor</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
@@ -15494,7 +15498,11 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H400" t="inlineStr"/>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>UiUtils.contrastingShade(activeComponentHoverColor, 8)</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -15515,24 +15523,20 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>thinBorderWidth</t>
+          <t>menuBarBackground</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H401" t="inlineStr">
-        <is>
-          <t>thinBorderWidth + "px"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -15548,17 +15552,17 @@
       <c r="C402" t="inlineStr"/>
       <c r="D402" t="inlineStr">
         <is>
-          <t>.menu-bar</t>
+          <t>.context-menu</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-border-color</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>menuBarBackground</t>
+          <t>thinBorderColor</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
@@ -15582,25 +15586,29 @@
       <c r="C403" t="inlineStr"/>
       <c r="D403" t="inlineStr">
         <is>
-          <t>.menu-button</t>
+          <t>.context-menu</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>-fx-padding</t>
+          <t>-fx-border-width</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>menuButtonPadding</t>
+          <t>thinBorderWidth</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>← font × 0,3 / 0,4</t>
-        </is>
-      </c>
-      <c r="H403" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>thinBorderWidth + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -15616,17 +15624,17 @@
       <c r="C404" t="inlineStr"/>
       <c r="D404" t="inlineStr">
         <is>
-          <t>.menu-item</t>
+          <t>.menu-bar</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>-fx-font-family</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>menuBarBackground</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
@@ -15634,11 +15642,7 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H404" t="inlineStr">
-        <is>
-          <t>"'" + font.getFamily() + "'"</t>
-        </is>
-      </c>
+      <c r="H404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -15654,7 +15658,7 @@
       <c r="C405" t="inlineStr"/>
       <c r="D405" t="inlineStr">
         <is>
-          <t>.menu-item</t>
+          <t>.menu-button</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -15664,12 +15668,12 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>menuItemPadding</t>
+          <t>menuButtonPadding</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>← font × 0,1 / 0,5</t>
+          <t>← font × 0,3 / 0,4</t>
         </is>
       </c>
       <c r="H405" t="inlineStr"/>
@@ -15685,24 +15689,20 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C406" t="inlineStr">
-        <is>
-          <t>:disabled</t>
-        </is>
-      </c>
+      <c r="C406" t="inlineStr"/>
       <c r="D406" t="inlineStr">
         <is>
-          <t>.menu-item:disabled .label</t>
+          <t>.menu-item</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>-fx-text-fill</t>
+          <t>-fx-font-family</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>textColor</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
@@ -15710,7 +15710,11 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H406" t="inlineStr"/>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>"'" + font.getFamily() + "'"</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -15723,36 +15727,28 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C407" t="inlineStr">
-        <is>
-          <t>:disabled, :hover</t>
-        </is>
-      </c>
+      <c r="C407" t="inlineStr"/>
       <c r="D407" t="inlineStr">
         <is>
-          <t>.menu-item:disabled:hover</t>
+          <t>.menu-item</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-padding</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>menuItemPadding</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H407" t="inlineStr">
-        <is>
-          <t>"transparent"</t>
-        </is>
-      </c>
+          <t>← font × 0,1 / 0,5</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -15767,27 +15763,27 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>:focused</t>
+          <t>:disabled</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>.menu-item:focused</t>
+          <t>.menu-item:disabled .label</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-text-fill</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>menuBarHoverBackground</t>
+          <t>textColor</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>← contrastingShade(menuBarBackground, 20)</t>
+          <t>Pflicht</t>
         </is>
       </c>
       <c r="H408" t="inlineStr"/>
@@ -15805,12 +15801,12 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>:hover</t>
+          <t>:disabled, :hover</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>.menu-item:hover</t>
+          <t>.menu-item:disabled:hover</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
@@ -15820,15 +15816,19 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>menuBarHoverBackground</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>← contrastingShade(menuBarBackground, 20)</t>
-        </is>
-      </c>
-      <c r="H409" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>"transparent"</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -15843,12 +15843,12 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>:hover</t>
+          <t>:focused</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>.menu:hover</t>
+          <t>.menu-item:focused</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
@@ -15881,12 +15881,12 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>:showing</t>
+          <t>:hover</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>.menu:showing</t>
+          <t>.menu-item:hover</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -15917,32 +15917,32 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>:hover</t>
+        </is>
+      </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>.my-spacer</t>
+          <t>.menu:hover</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>-fx-opacity</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>menuBarHoverBackground</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H412" t="inlineStr">
-        <is>
-          <t>"0"</t>
-        </is>
-      </c>
+          <t>← contrastingShade(menuBarBackground, 20)</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -15955,37 +15955,37 @@
           <t>überall</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr"/>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>:showing</t>
+        </is>
+      </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>.my-spacer</t>
+          <t>.menu:showing</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>-fx-pref-height</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>font</t>
+          <t>menuBarHoverBackground</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H413" t="inlineStr">
-        <is>
-          <t>"" + font.getSize() * 0.3 + "px"</t>
-        </is>
-      </c>
+          <t>← contrastingShade(menuBarBackground, 20)</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Titelleiste des Hauptfensters</t>
+          <t>Menü</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -15996,30 +15996,34 @@
       <c r="C414" t="inlineStr"/>
       <c r="D414" t="inlineStr">
         <is>
-          <t>.my-header-bar</t>
+          <t>.my-spacer</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>-fx-background-color</t>
+          <t>-fx-opacity</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>menuBarBackground</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H414" t="inlineStr"/>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>"0"</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Titelleiste des Hauptfensters</t>
+          <t>Menü</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -16030,17 +16034,17 @@
       <c r="C415" t="inlineStr"/>
       <c r="D415" t="inlineStr">
         <is>
-          <t>.my-header-bar</t>
+          <t>.my-spacer</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>-fx-border-color</t>
+          <t>-fx-pref-height</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>thinBorderColor</t>
+          <t>font</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
@@ -16048,7 +16052,11 @@
           <t>Pflicht</t>
         </is>
       </c>
-      <c r="H415" t="inlineStr"/>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>"" + font.getSize() * 0.3 + "px"</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -16069,24 +16077,20 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>-fx-border-width</t>
+          <t>-fx-background-color</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>menuBarBackground</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>fest im Code</t>
-        </is>
-      </c>
-      <c r="H416" t="inlineStr">
-        <is>
-          <t>"0 0 1 0"</t>
-        </is>
-      </c>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -16102,32 +16106,104 @@
       <c r="C417" t="inlineStr"/>
       <c r="D417" t="inlineStr">
         <is>
+          <t>.my-header-bar</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>-fx-border-color</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>thinBorderColor</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Titelleiste des Hauptfensters</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>überall</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>.my-header-bar</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>-fx-border-width</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>fest im Code</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>"0 0 1 0"</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Titelleiste des Hauptfensters</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>überall</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
           <t>.my-header-leading</t>
         </is>
       </c>
-      <c r="E417" t="inlineStr">
+      <c r="E419" t="inlineStr">
         <is>
           <t>-fx-padding</t>
         </is>
       </c>
-      <c r="F417" t="inlineStr">
+      <c r="F419" t="inlineStr">
         <is>
           <t>font</t>
         </is>
       </c>
-      <c r="G417" t="inlineStr">
-        <is>
-          <t>Pflicht</t>
-        </is>
-      </c>
-      <c r="H417" t="inlineStr">
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>Pflicht</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
         <is>
           <t>"0 0 0 " + (font.getSize() * 0.5) + "px"</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H417"/>
+  <autoFilter ref="A1:H419"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>